--- a/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>CTGO</t>
   </si>
@@ -656,140 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -880,8 +887,14 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -972,8 +985,14 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1083,14 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,55 +1123,57 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>900</v>
+      </c>
+      <c r="F12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>4500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>2100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
-      </c>
-      <c r="N12" s="3">
-        <v>100</v>
       </c>
       <c r="O12" s="3">
         <v>100</v>
       </c>
       <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>100</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>4</v>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1315,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1291,28 +1330,28 @@
         <v>4</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
+        <v>800</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
@@ -1326,11 +1365,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1406,11 +1451,11 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>4</v>
@@ -1424,11 +1469,11 @@
       <c r="R15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,100 +1548,108 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F17" s="3">
         <v>4000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>900</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>800</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>700</v>
       </c>
       <c r="AC17" s="3">
         <v>800</v>
       </c>
       <c r="AD17" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF17" s="3">
         <v>500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,91 +1657,97 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-3700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-6700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-6900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-700</v>
       </c>
       <c r="AC18" s="3">
         <v>-800</v>
       </c>
       <c r="AD18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,8 +1780,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1724,74 +1791,74 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="G20" s="3">
         <v>-6100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-5100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-9300</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>39400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1807,8 +1874,14 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1816,35 +1889,35 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="G21" s="3">
         <v>-9800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-7400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-13800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-6600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-6900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-6900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1899,44 +1972,50 @@
       <c r="AF21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F22" s="3">
         <v>900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
-      </c>
-      <c r="F22" s="3">
-        <v>500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>400</v>
       </c>
       <c r="H22" s="3">
         <v>500</v>
       </c>
       <c r="I22" s="3">
+        <v>400</v>
+      </c>
+      <c r="J22" s="3">
+        <v>500</v>
+      </c>
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1949,11 +2028,11 @@
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1991,111 +2070,123 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-13100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-10400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-7900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-14300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-7200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-6900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>35800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-2900</v>
       </c>
       <c r="T23" s="3">
         <v>-1900</v>
       </c>
       <c r="U23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W23" s="3">
         <v>-2100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-700</v>
       </c>
       <c r="AC23" s="3">
         <v>-800</v>
       </c>
       <c r="AD23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -2107,40 +2198,40 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2400</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>4</v>
@@ -2148,8 +2239,8 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-13100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-10400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-7900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-14300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-6800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>33400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-2900</v>
       </c>
       <c r="T26" s="3">
         <v>-1900</v>
       </c>
       <c r="U26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W26" s="3">
         <v>-2100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-700</v>
       </c>
       <c r="AC26" s="3">
         <v>-800</v>
       </c>
       <c r="AD26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-13100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-10400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-7900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-14300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-7200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-6800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-4500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>33400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2500</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-2900</v>
       </c>
       <c r="T27" s="3">
         <v>-1900</v>
       </c>
       <c r="U27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W27" s="3">
         <v>-2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-700</v>
       </c>
       <c r="AC27" s="3">
         <v>-800</v>
       </c>
       <c r="AD27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,8 +2952,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2828,74 +2967,74 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G32" s="3">
         <v>6100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>5100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>9300</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-39400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>2400</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -2911,100 +3050,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-13100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-10400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-7900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-14300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-7200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-6800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-4500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>33400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2500</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-2900</v>
       </c>
       <c r="T33" s="3">
         <v>-1900</v>
       </c>
       <c r="U33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W33" s="3">
         <v>-2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-700</v>
       </c>
       <c r="AC33" s="3">
         <v>-800</v>
       </c>
       <c r="AD33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-13100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-10400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-7900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-14300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-7200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-6800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-4500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>33400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2500</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-2900</v>
       </c>
       <c r="T35" s="3">
         <v>-1900</v>
       </c>
       <c r="U35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W35" s="3">
         <v>-2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-700</v>
       </c>
       <c r="AC35" s="3">
         <v>-800</v>
       </c>
       <c r="AD35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F41" s="3">
         <v>18500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>11600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>23100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>21900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>26800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>35200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>26200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>31900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>36400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>5400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>7600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>8600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>9800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>10400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>11700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>13800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>16600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>15800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>4900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>5200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>5600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>5800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,47 +3715,53 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
       </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3586,11 +3771,11 @@
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,204 +3911,222 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F45" s="3">
         <v>1600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>200</v>
-      </c>
-      <c r="T45" s="3">
-        <v>0</v>
       </c>
       <c r="U45" s="3">
         <v>200</v>
       </c>
       <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
         <v>200</v>
-      </c>
-      <c r="W45" s="3">
-        <v>100</v>
       </c>
       <c r="X45" s="3">
         <v>200</v>
       </c>
       <c r="Y45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
         <v>200</v>
       </c>
       <c r="AA45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB45" s="3">
         <v>200</v>
       </c>
       <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
-      <c r="AF45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>16900</v>
+      </c>
+      <c r="F46" s="3">
         <v>20100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>12300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>9800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>18500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>23800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>23700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>27800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>35900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>26800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>32400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>36600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>5500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>7600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>8800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>10000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>10500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>11800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>14000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>16800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>15900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>5100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>5400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>5700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>5900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>28100</v>
+      </c>
+      <c r="F47" s="3">
         <v>21400</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
       <c r="G47" s="3">
         <v>0</v>
       </c>
@@ -3996,16 +4205,22 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="E48" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="F48" s="3">
         <v>13400</v>
@@ -4014,28 +4229,28 @@
         <v>13400</v>
       </c>
       <c r="H48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="J48" s="3">
         <v>13500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>13500</v>
-      </c>
-      <c r="J48" s="3">
-        <v>13600</v>
-      </c>
-      <c r="K48" s="3">
-        <v>13600</v>
       </c>
       <c r="L48" s="3">
         <v>13600</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
+        <v>13600</v>
+      </c>
+      <c r="N48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
@@ -4046,11 +4261,11 @@
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -4088,8 +4303,14 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,31 +4597,37 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>58600</v>
+      </c>
+      <c r="F54" s="3">
         <v>54900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>25700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>17500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>23300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>32000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>37300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>23600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>37400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>41500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>36000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>26800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>32400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>36600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>7600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>8800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>10000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>10500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>11800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>14000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>16800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>15900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>5100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>5400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>5700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>5900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,70 +4967,72 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>300</v>
+      </c>
+      <c r="F57" s="3">
         <v>2100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>100</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
       </c>
       <c r="H57" s="3">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>200</v>
+      </c>
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>100</v>
-      </c>
-      <c r="V57" s="3">
-        <v>200</v>
-      </c>
-      <c r="W57" s="3">
-        <v>0</v>
       </c>
       <c r="X57" s="3">
         <v>200</v>
@@ -4780,7 +5041,7 @@
         <v>0</v>
       </c>
       <c r="Z57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
@@ -4789,31 +5050,37 @@
         <v>0</v>
       </c>
       <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3">
         <v>100</v>
       </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
       <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F58" s="3">
         <v>2000</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4826,18 +5093,18 @@
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3">
         <v>6300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>6300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4850,11 +5117,11 @@
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -4892,85 +5159,91 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
-      </c>
-      <c r="K59" s="3">
-        <v>200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>400</v>
       </c>
       <c r="M59" s="3">
         <v>200</v>
       </c>
       <c r="N59" s="3">
+        <v>400</v>
+      </c>
+      <c r="O59" s="3">
+        <v>200</v>
+      </c>
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>300</v>
-      </c>
-      <c r="V59" s="3">
-        <v>100</v>
-      </c>
-      <c r="W59" s="3">
-        <v>100</v>
       </c>
       <c r="X59" s="3">
         <v>100</v>
       </c>
       <c r="Y59" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA59" s="3">
         <v>200</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>100</v>
-      </c>
       <c r="AB59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="3">
         <v>100</v>
@@ -4982,84 +5255,90 @@
         <v>100</v>
       </c>
       <c r="AF59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>13100</v>
+      </c>
+      <c r="F60" s="3">
         <v>5000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>300</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>100</v>
       </c>
       <c r="AB60" s="3">
         <v>100</v>
@@ -5071,40 +5350,46 @@
         <v>100</v>
       </c>
       <c r="AE60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG60" s="3">
         <v>200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>36800</v>
+      </c>
+      <c r="F61" s="3">
         <v>32900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>25500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>19400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>19400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>19300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>19200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5168,22 +5453,28 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F62" s="3">
         <v>6000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2700</v>
-      </c>
-      <c r="F62" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3300</v>
       </c>
       <c r="H62" s="3">
         <v>3300</v>
@@ -5201,10 +5492,10 @@
         <v>3300</v>
       </c>
       <c r="M62" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="N62" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="O62" s="3">
         <v>1200</v>
@@ -5212,11 +5503,11 @@
       <c r="P62" s="3">
         <v>1200</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
+      <c r="Q62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R62" s="3">
+        <v>1200</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
@@ -5230,11 +5521,11 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,82 +5845,88 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>100200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>73100</v>
+      </c>
+      <c r="F66" s="3">
         <v>43800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>30400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>23300</v>
-      </c>
-      <c r="G66" s="3">
-        <v>24000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>24900</v>
       </c>
       <c r="I66" s="3">
         <v>24000</v>
       </c>
       <c r="J66" s="3">
+        <v>24900</v>
+      </c>
+      <c r="K66" s="3">
+        <v>24000</v>
+      </c>
+      <c r="L66" s="3">
         <v>4500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>10100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>10500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>300</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>100</v>
       </c>
       <c r="AB66" s="3">
         <v>100</v>
@@ -5623,13 +5938,19 @@
         <v>100</v>
       </c>
       <c r="AE66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG66" s="3">
         <v>200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-159500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-111400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-98300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-87900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-79900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-65600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-58500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-51300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-44500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-39600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-35000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-33200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-28700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-58900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-56300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-54400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-51500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-49700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-47500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-46100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-44200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-41300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-37500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-36600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-35800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-35100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-34300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-33800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-33200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="F76" s="3">
         <v>11000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-4800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-5700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>13300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>19100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>27300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>31000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>34500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>24400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>28800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>31100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>7200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>8300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>9800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>10500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>11600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>13700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>16800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>15800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>5000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-13100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-10400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-7900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-14300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-7200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-6800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-4500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>33400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2500</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-2900</v>
       </c>
       <c r="T81" s="3">
         <v>-1900</v>
       </c>
       <c r="U81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W81" s="3">
         <v>-2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-700</v>
       </c>
       <c r="AC81" s="3">
         <v>-800</v>
       </c>
       <c r="AD81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6837,11 +7234,11 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
@@ -6855,11 +7252,11 @@
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-5300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-5300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3300</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-200</v>
       </c>
       <c r="R89" s="3">
         <v>-700</v>
       </c>
       <c r="S89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-400</v>
       </c>
       <c r="X89" s="3">
         <v>-200</v>
       </c>
       <c r="Y89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-400</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-500</v>
       </c>
       <c r="AF89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7515,11 +7956,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
@@ -7533,11 +7974,11 @@
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,80 +8212,86 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-27000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-6700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-5100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-9300</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-7800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-6600</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-2500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>31000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>4</v>
       </c>
@@ -7842,17 +8301,23 @@
       <c r="AC94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,67 +8738,73 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F100" s="3">
         <v>37500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>16600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>2300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>5600</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>19800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>10900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-900</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>3200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -8325,28 +8816,34 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>1100</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F102" s="3">
         <v>6900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>8700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-5800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-9000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>15100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-13900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-8200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>9000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-5700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-4400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>33400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-700</v>
       </c>
       <c r="W102" s="3">
         <v>-1200</v>
       </c>
       <c r="X102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>10900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>4700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>CTGO</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -893,8 +897,11 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1134,37 +1148,37 @@
         <v>200</v>
       </c>
       <c r="E12" s="3">
+        <v>200</v>
+      </c>
+      <c r="F12" s="3">
         <v>900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>4500</v>
       </c>
       <c r="K12" s="3">
         <v>4500</v>
       </c>
       <c r="L12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="M12" s="3">
         <v>2100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1100</v>
-      </c>
-      <c r="O12" s="3">
-        <v>100</v>
       </c>
       <c r="P12" s="3">
         <v>100</v>
@@ -1173,10 +1187,10 @@
         <v>100</v>
       </c>
       <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>4</v>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,40 +1338,43 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
@@ -1371,8 +1391,8 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1457,8 +1480,8 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>4</v>
@@ -1475,8 +1498,8 @@
       <c r="T15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,106 +1576,110 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1300</v>
-      </c>
-      <c r="X17" s="3">
-        <v>1100</v>
       </c>
       <c r="Y17" s="3">
         <v>1100</v>
       </c>
       <c r="Z17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA17" s="3">
         <v>1000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1657,97 +1687,100 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-1100</v>
       </c>
       <c r="Y18" s="3">
         <v>-1100</v>
       </c>
       <c r="Z18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1791,77 +1825,77 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="F20" s="3">
         <v>-21200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>39400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-900</v>
       </c>
       <c r="W20" s="3">
         <v>-900</v>
       </c>
       <c r="X20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1880,8 +1914,11 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1889,38 +1926,38 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-26100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-12300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6600</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-6900</v>
       </c>
       <c r="L21" s="3">
         <v>-6900</v>
       </c>
       <c r="M21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="N21" s="3">
         <v>-4900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1978,47 +2015,50 @@
       <c r="AH21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E22" s="3">
         <v>2000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2034,8 +2074,8 @@
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -2076,106 +2116,112 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-20500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>35800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2188,8 +2234,8 @@
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -2204,29 +2250,29 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2400</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2236,14 +2282,14 @@
       <c r="V24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-27600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>33400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-20500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-27600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>33400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2967,77 +3037,77 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F32" s="3">
         <v>21200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-39400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1800</v>
-      </c>
-      <c r="V32" s="3">
-        <v>900</v>
       </c>
       <c r="W32" s="3">
         <v>900</v>
       </c>
       <c r="X32" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2400</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-20500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>33400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-20500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>33400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E41" s="3">
         <v>7600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>35200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>31900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>36400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>15800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3751,20 +3844,20 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>500</v>
-      </c>
-      <c r="M43" s="3">
-        <v>300</v>
       </c>
       <c r="N43" s="3">
         <v>300</v>
       </c>
       <c r="O43" s="3">
+        <v>300</v>
+      </c>
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3777,8 +3870,8 @@
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,79 +4013,82 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>700</v>
       </c>
       <c r="K45" s="3">
         <v>700</v>
       </c>
       <c r="L45" s="3">
+        <v>700</v>
+      </c>
+      <c r="M45" s="3">
         <v>1500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
       <c r="W45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
         <v>200</v>
       </c>
       <c r="Y45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>200</v>
       </c>
       <c r="AA45" s="3">
         <v>200</v>
@@ -3998,138 +4097,144 @@
         <v>200</v>
       </c>
       <c r="AC45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD45" s="3">
         <v>100</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>200</v>
       </c>
       <c r="AE45" s="3">
         <v>200</v>
       </c>
       <c r="AF45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG45" s="3">
         <v>100</v>
       </c>
       <c r="AH45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E46" s="3">
         <v>9000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>27800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>26800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>32400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>36600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E47" s="3">
         <v>43400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>21400</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
       <c r="H47" s="3">
         <v>0</v>
       </c>
@@ -4211,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4223,7 +4331,7 @@
         <v>13300</v>
       </c>
       <c r="F48" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="G48" s="3">
         <v>13400</v>
@@ -4235,13 +4343,13 @@
         <v>13400</v>
       </c>
       <c r="J48" s="3">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="K48" s="3">
         <v>13500</v>
       </c>
       <c r="L48" s="3">
-        <v>13600</v>
+        <v>13500</v>
       </c>
       <c r="M48" s="3">
         <v>13600</v>
@@ -4250,10 +4358,10 @@
         <v>13600</v>
       </c>
       <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
+        <v>13600</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
@@ -4267,8 +4375,8 @@
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,19 +4720,22 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
+      <c r="F52" s="3">
+        <v>400</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>4</v>
@@ -4629,8 +4749,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E54" s="3">
         <v>66200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>58600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>54900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>36600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>14000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,83 +5099,84 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>600</v>
       </c>
       <c r="L57" s="3">
         <v>600</v>
       </c>
       <c r="M57" s="3">
+        <v>600</v>
+      </c>
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
       <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
         <v>200</v>
-      </c>
-      <c r="V57" s="3">
-        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>100</v>
       </c>
       <c r="X57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y57" s="3">
         <v>200</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
       <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
-      </c>
       <c r="AB57" s="3">
         <v>0</v>
       </c>
@@ -5056,34 +5187,37 @@
         <v>0</v>
       </c>
       <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3">
         <v>100</v>
       </c>
-      <c r="AF57" s="3">
-        <v>0</v>
-      </c>
       <c r="AG57" s="3">
         <v>0</v>
       </c>
       <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E58" s="3">
         <v>21700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2000</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5099,14 +5233,14 @@
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M58" s="3">
-        <v>6300</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>6300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
+      <c r="O58" s="3">
+        <v>6300</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
@@ -5123,8 +5257,8 @@
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -5165,73 +5299,76 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E59" s="3">
         <v>10600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1000</v>
-      </c>
-      <c r="T59" s="3">
-        <v>200</v>
       </c>
       <c r="U59" s="3">
         <v>200</v>
       </c>
       <c r="V59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W59" s="3">
         <v>300</v>
       </c>
       <c r="X59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Y59" s="3">
         <v>100</v>
@@ -5240,13 +5377,13 @@
         <v>100</v>
       </c>
       <c r="AA59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB59" s="3">
         <v>200</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
-      </c>
       <c r="AC59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="3">
         <v>100</v>
@@ -5261,87 +5398,90 @@
         <v>100</v>
       </c>
       <c r="AH59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E60" s="3">
         <v>32700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>300</v>
-      </c>
-      <c r="V60" s="3">
-        <v>400</v>
       </c>
       <c r="W60" s="3">
         <v>400</v>
       </c>
       <c r="X60" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y60" s="3">
         <v>200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>100</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>300</v>
       </c>
       <c r="AA60" s="3">
         <v>300</v>
       </c>
       <c r="AB60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AC60" s="3">
         <v>100</v>
@@ -5356,43 +5496,46 @@
         <v>100</v>
       </c>
       <c r="AG60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH60" s="3">
         <v>200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E61" s="3">
         <v>35400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25500</v>
-      </c>
-      <c r="H61" s="3">
-        <v>19400</v>
       </c>
       <c r="I61" s="3">
         <v>19400</v>
       </c>
       <c r="J61" s="3">
+        <v>19400</v>
+      </c>
+      <c r="K61" s="3">
         <v>19300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5459,25 +5602,28 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E62" s="3">
         <v>32100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3300</v>
       </c>
       <c r="I62" s="3">
         <v>3300</v>
@@ -5498,7 +5644,7 @@
         <v>3300</v>
       </c>
       <c r="O62" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="P62" s="3">
         <v>1200</v>
@@ -5509,8 +5655,8 @@
       <c r="R62" s="3">
         <v>1200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
+      <c r="S62" s="3">
+        <v>1200</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
@@ -5527,8 +5673,8 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,85 +6006,88 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E66" s="3">
         <v>100200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>73100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>43800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>300</v>
-      </c>
-      <c r="V66" s="3">
-        <v>400</v>
       </c>
       <c r="W66" s="3">
         <v>400</v>
       </c>
       <c r="X66" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y66" s="3">
         <v>200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>100</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>300</v>
       </c>
       <c r="AA66" s="3">
         <v>300</v>
       </c>
       <c r="AB66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AC66" s="3">
         <v>100</v>
@@ -5944,13 +6102,16 @@
         <v>100</v>
       </c>
       <c r="AG66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH66" s="3">
         <v>200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-178100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-159500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-139000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-111400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-98300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-87900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-79900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-65600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-58500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-51300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-44500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-39600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-35000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-33200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-28700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-25500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-58900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-56300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-54400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-51500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-49700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-47500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-46100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-44200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-41300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-37500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-36600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-35800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-35100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-34300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-33800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-33200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-37900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-34000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-14500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-4800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-5700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>31000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>34500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>31100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-20500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>33400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7240,8 +7439,8 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
@@ -7258,8 +7457,8 @@
       <c r="T83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-5300</v>
       </c>
       <c r="J89" s="3">
         <v>-5300</v>
       </c>
       <c r="K89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="L89" s="3">
         <v>-4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-100</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-200</v>
       </c>
       <c r="X89" s="3">
         <v>-200</v>
       </c>
       <c r="Y89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-300</v>
       </c>
       <c r="AB89" s="3">
         <v>-300</v>
       </c>
       <c r="AC89" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AD89" s="3">
         <v>-200</v>
       </c>
       <c r="AE89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7962,8 +8183,8 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>4</v>
@@ -7980,8 +8201,8 @@
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,83 +8445,86 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9300</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-7800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6600</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>31000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1800</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-900</v>
       </c>
       <c r="W94" s="3">
         <v>-900</v>
       </c>
       <c r="X94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8307,8 +8537,8 @@
       <c r="AE94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,61 +8987,64 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E100" s="3">
         <v>12000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>37500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>16600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5600</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>19800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>10900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-900</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>3200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>4</v>
@@ -8806,8 +9052,8 @@
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -8822,28 +9068,31 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>1100</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
+      <c r="AG100" s="3">
+        <v>0</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>33400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>10900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>CTGO</t>
   </si>
@@ -656,174 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45291</v>
       </c>
       <c r="G7" s="2">
         <v>45199</v>
       </c>
       <c r="H7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
       <c r="J7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -900,8 +903,11 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1001,8 +1007,11 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1102,8 +1111,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,49 +1151,50 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>200</v>
-      </c>
-      <c r="E12" s="3">
-        <v>200</v>
-      </c>
-      <c r="F12" s="3">
-        <v>900</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>400</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="3">
         <v>2300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>4500</v>
       </c>
       <c r="L12" s="3">
         <v>4500</v>
       </c>
       <c r="M12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="N12" s="3">
         <v>2100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>100</v>
       </c>
       <c r="Q12" s="3">
         <v>100</v>
@@ -1190,10 +1203,10 @@
         <v>100</v>
       </c>
       <c r="S12" s="3">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>4</v>
@@ -1240,8 +1253,11 @@
       <c r="AI12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,43 +1357,46 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>800</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
@@ -1394,8 +1413,8 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1442,8 +1461,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1483,8 +1505,8 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>4</v>
@@ -1501,8 +1523,8 @@
       <c r="U15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1543,8 +1565,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1602,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2700</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4900</v>
       </c>
       <c r="G17" s="3">
         <v>4000</v>
       </c>
       <c r="H17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3700</v>
       </c>
-      <c r="I17" s="3">
-        <v>2400</v>
-      </c>
       <c r="J17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1300</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1100</v>
       </c>
       <c r="Z17" s="3">
         <v>1100</v>
       </c>
       <c r="AA17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB17" s="3">
         <v>1000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-5800</v>
       </c>
       <c r="E18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-4900</v>
       </c>
       <c r="G18" s="3">
         <v>-4000</v>
       </c>
       <c r="H18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-3700</v>
       </c>
-      <c r="I18" s="3">
-        <v>-2400</v>
-      </c>
       <c r="J18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z18" s="3">
         <v>-1100</v>
       </c>
       <c r="AA18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,89 +1848,90 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
-        <v>-15800</v>
+        <v>13200</v>
       </c>
       <c r="F20" s="3">
-        <v>-21200</v>
+        <v>15800</v>
       </c>
       <c r="G20" s="3">
-        <v>-8300</v>
+        <v>8300</v>
       </c>
       <c r="H20" s="3">
-        <v>-6100</v>
+        <v>8300</v>
       </c>
       <c r="I20" s="3">
-        <v>-5100</v>
+        <v>6100</v>
       </c>
       <c r="J20" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-9300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>39400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-900</v>
       </c>
       <c r="X20" s="3">
         <v>-900</v>
       </c>
       <c r="Y20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1917,50 +1950,53 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-5100</v>
       </c>
       <c r="E21" s="3">
-        <v>-18400</v>
+        <v>-15600</v>
       </c>
       <c r="F21" s="3">
-        <v>-26100</v>
+        <v>-18500</v>
       </c>
       <c r="G21" s="3">
         <v>-12300</v>
       </c>
       <c r="H21" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-9800</v>
       </c>
-      <c r="I21" s="3">
-        <v>-7400</v>
-      </c>
       <c r="J21" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-13800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-6900</v>
       </c>
       <c r="M21" s="3">
         <v>-6900</v>
       </c>
       <c r="N21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="O21" s="3">
         <v>-4900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2018,50 +2054,53 @@
       <c r="AI21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E22" s="3">
         <v>2900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
-        <v>1500</v>
-      </c>
       <c r="G22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H22" s="3">
+        <v>800</v>
+      </c>
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
+        <v>600</v>
+      </c>
+      <c r="K22" s="3">
+        <v>400</v>
+      </c>
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
-        <v>400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>500</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2077,8 +2116,8 @@
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2119,114 +2158,120 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-20500</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-27600</v>
       </c>
       <c r="G23" s="3">
         <v>-13100</v>
       </c>
       <c r="H23" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="I23" s="3">
         <v>-10400</v>
       </c>
-      <c r="I23" s="3">
-        <v>-7900</v>
-      </c>
       <c r="J23" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-14300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>35800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
+      <c r="D24" s="3">
+        <v>700</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>4</v>
@@ -2237,14 +2282,14 @@
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2253,29 +2298,29 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2400</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2285,14 +2330,14 @@
       <c r="W24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -2321,8 +2366,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2470,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-18500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-20500</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-27600</v>
       </c>
       <c r="G26" s="3">
         <v>-13100</v>
       </c>
       <c r="H26" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="I26" s="3">
         <v>-10400</v>
       </c>
-      <c r="I26" s="3">
-        <v>-7900</v>
-      </c>
       <c r="J26" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-14300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>33400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-18500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20500</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-27600</v>
       </c>
       <c r="G27" s="3">
         <v>-13100</v>
       </c>
       <c r="H27" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="I27" s="3">
         <v>-10400</v>
       </c>
-      <c r="I27" s="3">
-        <v>-7900</v>
-      </c>
       <c r="J27" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-14300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>33400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2782,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2886,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,89 +3094,92 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>600</v>
       </c>
       <c r="E32" s="3">
-        <v>15800</v>
+        <v>-13200</v>
       </c>
       <c r="F32" s="3">
-        <v>21200</v>
+        <v>-15800</v>
       </c>
       <c r="G32" s="3">
-        <v>8300</v>
+        <v>-8300</v>
       </c>
       <c r="H32" s="3">
-        <v>6100</v>
+        <v>-8300</v>
       </c>
       <c r="I32" s="3">
-        <v>5100</v>
+        <v>-6100</v>
       </c>
       <c r="J32" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="K32" s="3">
         <v>9300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>1500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-39400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1800</v>
-      </c>
-      <c r="W32" s="3">
-        <v>900</v>
       </c>
       <c r="X32" s="3">
         <v>900</v>
       </c>
       <c r="Y32" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2400</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3129,109 +3198,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-18500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20500</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-27600</v>
       </c>
       <c r="G33" s="3">
         <v>-13100</v>
       </c>
       <c r="H33" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="I33" s="3">
         <v>-10400</v>
       </c>
-      <c r="I33" s="3">
-        <v>-7900</v>
-      </c>
       <c r="J33" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-14300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>33400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3406,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-18500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20500</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-27600</v>
       </c>
       <c r="G35" s="3">
         <v>-13100</v>
       </c>
       <c r="H35" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="I35" s="3">
         <v>-10400</v>
       </c>
-      <c r="I35" s="3">
-        <v>-7900</v>
-      </c>
       <c r="J35" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-14300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>33400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45291</v>
       </c>
       <c r="G38" s="2">
         <v>45199</v>
       </c>
       <c r="H38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
       <c r="J38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3697,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E41" s="3">
         <v>24100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7600</v>
-      </c>
-      <c r="F41" s="3">
-        <v>15500</v>
       </c>
       <c r="G41" s="3">
         <v>18500</v>
       </c>
       <c r="H41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I41" s="3">
         <v>11600</v>
       </c>
-      <c r="I41" s="3">
-        <v>2900</v>
-      </c>
       <c r="J41" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K41" s="3">
         <v>8800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>26800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>26200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>31900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,31 +3903,34 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3847,20 +3939,20 @@
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>500</v>
-      </c>
-      <c r="N43" s="3">
-        <v>300</v>
       </c>
       <c r="O43" s="3">
         <v>300</v>
       </c>
       <c r="P43" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3873,8 +3965,8 @@
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3915,31 +4007,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,82 +4111,85 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1300</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G45" s="3">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="H45" s="3">
-        <v>600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J45" s="3">
+        <v>500</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>1000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>700</v>
       </c>
       <c r="L45" s="3">
         <v>700</v>
       </c>
       <c r="M45" s="3">
+        <v>700</v>
+      </c>
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
       <c r="X45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>200</v>
       </c>
       <c r="Z45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>200</v>
       </c>
       <c r="AB45" s="3">
         <v>200</v>
@@ -4100,149 +4198,155 @@
         <v>200</v>
       </c>
       <c r="AD45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE45" s="3">
         <v>100</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>200</v>
       </c>
       <c r="AF45" s="3">
         <v>200</v>
       </c>
       <c r="AG45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH45" s="3">
         <v>100</v>
       </c>
       <c r="AI45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E46" s="3">
         <v>25600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9000</v>
-      </c>
-      <c r="F46" s="3">
-        <v>16900</v>
       </c>
       <c r="G46" s="3">
         <v>20100</v>
       </c>
       <c r="H46" s="3">
+        <v>20100</v>
+      </c>
+      <c r="I46" s="3">
         <v>12300</v>
       </c>
-      <c r="I46" s="3">
-        <v>4100</v>
-      </c>
       <c r="J46" s="3">
+        <v>12300</v>
+      </c>
+      <c r="K46" s="3">
         <v>9800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>35900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>26800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>32400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E47" s="3">
         <v>54500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>43400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>28100</v>
       </c>
       <c r="G47" s="3">
         <v>21400</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>21400</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,13 +4423,16 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13300</v>
+        <v>52500</v>
       </c>
       <c r="E48" s="3">
         <v>13300</v>
@@ -4346,13 +4453,13 @@
         <v>13400</v>
       </c>
       <c r="K48" s="3">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="L48" s="3">
         <v>13500</v>
       </c>
       <c r="M48" s="3">
-        <v>13600</v>
+        <v>13500</v>
       </c>
       <c r="N48" s="3">
         <v>13600</v>
@@ -4361,10 +4468,10 @@
         <v>13600</v>
       </c>
       <c r="P48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
+        <v>13600</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
@@ -4378,8 +4485,8 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -4420,8 +4527,11 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4631,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,16 +4839,19 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
         <v>300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>400</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
@@ -4752,8 +4871,8 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4824,8 +4943,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5047,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>158300</v>
+      </c>
+      <c r="E54" s="3">
         <v>93600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>66200</v>
-      </c>
-      <c r="F54" s="3">
-        <v>58600</v>
       </c>
       <c r="G54" s="3">
         <v>54900</v>
       </c>
       <c r="H54" s="3">
+        <v>54900</v>
+      </c>
+      <c r="I54" s="3">
         <v>25700</v>
       </c>
-      <c r="I54" s="3">
-        <v>17500</v>
-      </c>
       <c r="J54" s="3">
+        <v>25700</v>
+      </c>
+      <c r="K54" s="3">
         <v>23300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>36600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>14000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>16800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>15900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,86 +5229,87 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
-      </c>
-      <c r="F57" s="3">
-        <v>300</v>
       </c>
       <c r="G57" s="3">
         <v>2100</v>
       </c>
       <c r="H57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>200</v>
       </c>
       <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
         <v>1200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>600</v>
       </c>
       <c r="M57" s="3">
         <v>600</v>
       </c>
       <c r="N57" s="3">
+        <v>600</v>
+      </c>
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>1900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
       <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
         <v>200</v>
-      </c>
-      <c r="W57" s="3">
-        <v>100</v>
       </c>
       <c r="X57" s="3">
         <v>100</v>
       </c>
       <c r="Y57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z57" s="3">
         <v>200</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
       <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
       <c r="AC57" s="3">
         <v>0</v>
       </c>
@@ -5190,42 +5320,45 @@
         <v>0</v>
       </c>
       <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
         <v>100</v>
       </c>
-      <c r="AG57" s="3">
-        <v>0</v>
-      </c>
       <c r="AH57" s="3">
         <v>0</v>
       </c>
       <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E58" s="3">
         <v>29900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>7900</v>
       </c>
       <c r="G58" s="3">
         <v>2000</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+      <c r="H58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
@@ -5236,14 +5369,14 @@
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
-        <v>6300</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>6300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
+      <c r="P58" s="3">
+        <v>6300</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
@@ -5260,8 +5393,8 @@
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -5302,76 +5435,79 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>19800</v>
+        <v>31000</v>
       </c>
       <c r="E59" s="3">
-        <v>10600</v>
+        <v>17900</v>
       </c>
       <c r="F59" s="3">
-        <v>4900</v>
-      </c>
-      <c r="G59" s="3">
+        <v>9500</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
+        <v>600</v>
+      </c>
+      <c r="O59" s="3">
+        <v>200</v>
+      </c>
+      <c r="P59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>200</v>
+      </c>
+      <c r="R59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
-        <v>900</v>
-      </c>
-      <c r="M59" s="3">
-        <v>600</v>
-      </c>
-      <c r="N59" s="3">
-        <v>200</v>
-      </c>
-      <c r="O59" s="3">
-        <v>400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
-      </c>
-      <c r="U59" s="3">
-        <v>200</v>
       </c>
       <c r="V59" s="3">
         <v>200</v>
       </c>
       <c r="W59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X59" s="3">
         <v>300</v>
       </c>
       <c r="Y59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Z59" s="3">
         <v>100</v>
@@ -5380,13 +5516,13 @@
         <v>100</v>
       </c>
       <c r="AB59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC59" s="3">
         <v>200</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
-      </c>
       <c r="AD59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE59" s="3">
         <v>100</v>
@@ -5401,90 +5537,93 @@
         <v>100</v>
       </c>
       <c r="AI59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E60" s="3">
         <v>50500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32700</v>
-      </c>
-      <c r="F60" s="3">
-        <v>13100</v>
       </c>
       <c r="G60" s="3">
         <v>5000</v>
       </c>
       <c r="H60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I60" s="3">
         <v>2300</v>
       </c>
-      <c r="I60" s="3">
-        <v>600</v>
-      </c>
       <c r="J60" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K60" s="3">
         <v>1400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>300</v>
-      </c>
-      <c r="W60" s="3">
-        <v>400</v>
       </c>
       <c r="X60" s="3">
         <v>400</v>
       </c>
       <c r="Y60" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z60" s="3">
         <v>200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>100</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>300</v>
       </c>
       <c r="AB60" s="3">
         <v>300</v>
       </c>
       <c r="AC60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AD60" s="3">
         <v>100</v>
@@ -5499,46 +5638,49 @@
         <v>100</v>
       </c>
       <c r="AH60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI60" s="3">
         <v>200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E61" s="3">
         <v>44700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35400</v>
-      </c>
-      <c r="F61" s="3">
-        <v>36800</v>
       </c>
       <c r="G61" s="3">
         <v>32900</v>
       </c>
       <c r="H61" s="3">
+        <v>32900</v>
+      </c>
+      <c r="I61" s="3">
         <v>25500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
+        <v>25500</v>
+      </c>
+      <c r="K61" s="3">
         <v>19400</v>
       </c>
-      <c r="J61" s="3">
-        <v>19400</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5605,31 +5747,34 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E62" s="3">
         <v>36300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>32100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>23300</v>
       </c>
       <c r="G62" s="3">
         <v>6000</v>
       </c>
       <c r="H62" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I62" s="3">
         <v>2700</v>
       </c>
-      <c r="I62" s="3">
-        <v>3300</v>
-      </c>
       <c r="J62" s="3">
-        <v>3300</v>
+        <v>2700</v>
       </c>
       <c r="K62" s="3">
         <v>3300</v>
@@ -5647,7 +5792,7 @@
         <v>3300</v>
       </c>
       <c r="P62" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="Q62" s="3">
         <v>1200</v>
@@ -5658,8 +5803,8 @@
       <c r="S62" s="3">
         <v>1200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
+      <c r="T62" s="3">
+        <v>1200</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
@@ -5676,8 +5821,8 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -5706,8 +5851,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,88 +6163,91 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>168500</v>
+      </c>
+      <c r="E66" s="3">
         <v>131500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>100200</v>
-      </c>
-      <c r="F66" s="3">
-        <v>73100</v>
       </c>
       <c r="G66" s="3">
         <v>43800</v>
       </c>
       <c r="H66" s="3">
+        <v>43800</v>
+      </c>
+      <c r="I66" s="3">
         <v>30400</v>
       </c>
-      <c r="I66" s="3">
-        <v>23300</v>
-      </c>
       <c r="J66" s="3">
+        <v>30400</v>
+      </c>
+      <c r="K66" s="3">
         <v>24000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>300</v>
-      </c>
-      <c r="W66" s="3">
-        <v>400</v>
       </c>
       <c r="X66" s="3">
         <v>400</v>
       </c>
       <c r="Y66" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z66" s="3">
         <v>200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>100</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>300</v>
       </c>
       <c r="AB66" s="3">
         <v>300</v>
       </c>
       <c r="AC66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AD66" s="3">
         <v>100</v>
@@ -6105,13 +6262,16 @@
         <v>100</v>
       </c>
       <c r="AH66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI66" s="3">
         <v>200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6721,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-187800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-178100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-159500</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-139000</v>
       </c>
       <c r="G72" s="3">
         <v>-111400</v>
       </c>
       <c r="H72" s="3">
+        <v>-111400</v>
+      </c>
+      <c r="I72" s="3">
         <v>-98300</v>
       </c>
-      <c r="I72" s="3">
-        <v>-87900</v>
-      </c>
       <c r="J72" s="3">
+        <v>-98300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-79900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-65600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-58500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-51300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-44500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-39600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-33200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-28700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-25500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-58900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-56300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-54400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-51500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-49700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-47500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-46100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-41300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-37500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-36600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-35800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-35100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-34300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-33800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-33200</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7137,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-37900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-34000</v>
-      </c>
-      <c r="F76" s="3">
-        <v>-14500</v>
       </c>
       <c r="G76" s="3">
         <v>11000</v>
       </c>
       <c r="H76" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I76" s="3">
         <v>-4800</v>
       </c>
-      <c r="I76" s="3">
-        <v>-5700</v>
-      </c>
       <c r="J76" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="K76" s="3">
         <v>-800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>31000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>34500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>28800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>31100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>16800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7345,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45291</v>
       </c>
       <c r="G80" s="2">
         <v>45199</v>
       </c>
       <c r="H80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
       <c r="J80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-18500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20500</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-27600</v>
       </c>
       <c r="G81" s="3">
         <v>-13100</v>
       </c>
       <c r="H81" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="I81" s="3">
         <v>-10400</v>
       </c>
-      <c r="I81" s="3">
-        <v>-7900</v>
-      </c>
       <c r="J81" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-14300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>33400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7598,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7442,8 +7640,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>4</v>
@@ -7460,8 +7658,8 @@
       <c r="U83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -7502,8 +7700,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8220,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4400</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-5900</v>
       </c>
       <c r="G89" s="3">
         <v>-3600</v>
       </c>
       <c r="H89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3">
-        <v>-3000</v>
-      </c>
       <c r="J89" s="3">
-        <v>-5300</v>
+        <v>-1100</v>
       </c>
       <c r="K89" s="3">
         <v>-5300</v>
       </c>
       <c r="L89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="M89" s="3">
         <v>-4700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-200</v>
       </c>
       <c r="Y89" s="3">
         <v>-200</v>
       </c>
       <c r="Z89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-300</v>
       </c>
       <c r="AC89" s="3">
         <v>-300</v>
       </c>
       <c r="AD89" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AE89" s="3">
         <v>-200</v>
       </c>
       <c r="AF89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8364,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8165,11 +8385,11 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8186,8 +8406,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
@@ -8204,8 +8424,8 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -8246,8 +8466,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,86 +8674,89 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15500</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-7400</v>
       </c>
       <c r="G94" s="3">
         <v>-27000</v>
       </c>
       <c r="H94" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-6700</v>
       </c>
-      <c r="I94" s="3">
-        <v>-5100</v>
-      </c>
       <c r="J94" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-9300</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-7800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6600</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-2500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>31000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1800</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-900</v>
       </c>
       <c r="X94" s="3">
         <v>-900</v>
       </c>
       <c r="Y94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8540,8 +8769,8 @@
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
@@ -8549,8 +8778,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8818,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8920,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,64 +9232,67 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E100" s="3">
         <v>30700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12000</v>
-      </c>
-      <c r="F100" s="3">
-        <v>10200</v>
       </c>
       <c r="G100" s="3">
         <v>37500</v>
       </c>
       <c r="H100" s="3">
+        <v>37500</v>
+      </c>
+      <c r="I100" s="3">
         <v>16600</v>
       </c>
-      <c r="I100" s="3">
-        <v>2300</v>
-      </c>
       <c r="J100" s="3">
+        <v>16600</v>
+      </c>
+      <c r="K100" s="3">
         <v>5600</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>19800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>10900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-900</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>3200</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>4</v>
@@ -9055,8 +9300,8 @@
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -9071,51 +9316,54 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>1100</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
+      <c r="AF100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>4</v>
+      <c r="AH100" s="3">
+        <v>0</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9440,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E102" s="3">
         <v>16500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7900</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-3000</v>
       </c>
       <c r="G102" s="3">
         <v>6900</v>
       </c>
       <c r="H102" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I102" s="3">
         <v>8700</v>
       </c>
-      <c r="I102" s="3">
-        <v>-5800</v>
-      </c>
       <c r="J102" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-9000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>33400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>10900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>CTGO</t>
   </si>
@@ -656,154 +656,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
-        <v>45107</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -828,8 +831,8 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -906,8 +909,11 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1010,8 +1016,11 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1114,8 +1123,11 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1152,8 +1164,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1178,26 +1191,26 @@
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3">
         <v>2300</v>
-      </c>
-      <c r="L12" s="3">
-        <v>4500</v>
       </c>
       <c r="M12" s="3">
         <v>4500</v>
       </c>
       <c r="N12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="O12" s="3">
         <v>2100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
       </c>
       <c r="R12" s="3">
         <v>100</v>
@@ -1206,10 +1219,10 @@
         <v>100</v>
       </c>
       <c r="T12" s="3">
-        <v>0</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>4</v>
@@ -1256,8 +1269,11 @@
       <c r="AJ12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,46 +1376,49 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
@@ -1416,8 +1435,8 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1464,8 +1483,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1508,8 +1530,8 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>4</v>
@@ -1526,8 +1548,8 @@
       <c r="V15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1568,8 +1590,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,216 +1628,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E17" s="3">
         <v>5800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I17" s="3">
         <v>4000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3700</v>
       </c>
-      <c r="J17" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1300</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>1100</v>
       </c>
       <c r="AA17" s="3">
         <v>1100</v>
       </c>
       <c r="AB17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC17" s="3">
         <v>1000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-4000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3700</v>
       </c>
-      <c r="J18" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-1100</v>
       </c>
       <c r="AA18" s="3">
         <v>-1100</v>
       </c>
       <c r="AB18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1849,92 +1881,93 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>13200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>15800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>21300</v>
+      </c>
+      <c r="I20" s="3">
         <v>8300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>8300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>6100</v>
       </c>
-      <c r="J20" s="3">
-        <v>6100</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>39400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-900</v>
       </c>
       <c r="Y20" s="3">
         <v>-900</v>
       </c>
       <c r="Z20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -1953,53 +1986,56 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-15600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-12300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-12300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-9800</v>
       </c>
-      <c r="J21" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6600</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-6900</v>
       </c>
       <c r="N21" s="3">
         <v>-6900</v>
       </c>
       <c r="O21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="P21" s="3">
         <v>-4900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2057,53 +2093,56 @@
       <c r="AJ21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E22" s="3">
         <v>3700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
-        <v>600</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2119,8 +2158,8 @@
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2161,121 +2200,127 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-20500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-13100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-13100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-10400</v>
       </c>
-      <c r="J23" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>35800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2291,8 +2336,8 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2301,29 +2346,29 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2400</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2333,14 +2378,14 @@
       <c r="X24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
@@ -2369,8 +2414,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,216 +2521,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-20500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="I26" s="3">
         <v>-13100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-13100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-10400</v>
       </c>
-      <c r="J26" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>33400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-20500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="I27" s="3">
         <v>-13100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-13100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-10400</v>
       </c>
-      <c r="J27" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>33400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2842,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2889,8 +2949,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3056,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,92 +3163,95 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-13200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-15800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-8300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-8300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-6100</v>
       </c>
-      <c r="J32" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-39400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1800</v>
-      </c>
-      <c r="X32" s="3">
-        <v>900</v>
       </c>
       <c r="Y32" s="3">
         <v>900</v>
       </c>
       <c r="Z32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2400</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3201,112 +3270,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-20500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="I33" s="3">
         <v>-13100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-13100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-10400</v>
       </c>
-      <c r="J33" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>33400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,221 +3484,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-20500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="I35" s="3">
         <v>-13100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-13100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-10400</v>
       </c>
-      <c r="J35" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>33400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
-        <v>45107</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3744,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,112 +3783,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E41" s="3">
         <v>36200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
+        <v>15500</v>
+      </c>
+      <c r="I41" s="3">
         <v>18500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>18500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>11600</v>
       </c>
-      <c r="J41" s="3">
-        <v>11600</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>21900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>26200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>31900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>36400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>16600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>15800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3906,13 +3995,16 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>600</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -3932,8 +4024,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3942,20 +4034,20 @@
         <v>0</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>500</v>
-      </c>
-      <c r="O43" s="3">
-        <v>300</v>
       </c>
       <c r="P43" s="3">
         <v>300</v>
       </c>
       <c r="Q43" s="3">
+        <v>300</v>
+      </c>
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3968,8 +4060,8 @@
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -4010,8 +4102,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4036,8 +4131,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4114,8 +4209,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4128,71 +4226,71 @@
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>1000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>700</v>
       </c>
       <c r="M45" s="3">
         <v>700</v>
       </c>
       <c r="N45" s="3">
+        <v>700</v>
+      </c>
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
       <c r="Y45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3">
         <v>200</v>
       </c>
       <c r="AA45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB45" s="3">
         <v>100</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>200</v>
       </c>
       <c r="AC45" s="3">
         <v>200</v>
@@ -4201,155 +4299,161 @@
         <v>200</v>
       </c>
       <c r="AE45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF45" s="3">
         <v>100</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>200</v>
       </c>
       <c r="AG45" s="3">
         <v>200</v>
       </c>
       <c r="AH45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AI45" s="3">
         <v>100</v>
       </c>
       <c r="AJ45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E46" s="3">
         <v>37500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>16900</v>
+      </c>
+      <c r="I46" s="3">
         <v>20100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>20100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>12300</v>
       </c>
-      <c r="J46" s="3">
-        <v>12300</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>27800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>35900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>26800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>32400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>36600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E47" s="3">
         <v>68300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>54500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>43400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
+        <v>28100</v>
+      </c>
+      <c r="I47" s="3">
         <v>21400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>21400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4426,25 +4530,28 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E48" s="3">
         <v>52500</v>
-      </c>
-      <c r="E48" s="3">
-        <v>13300</v>
       </c>
       <c r="F48" s="3">
         <v>13300</v>
       </c>
       <c r="G48" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="H48" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="I48" s="3">
         <v>13400</v>
@@ -4456,13 +4563,13 @@
         <v>13400</v>
       </c>
       <c r="L48" s="3">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="M48" s="3">
         <v>13500</v>
       </c>
       <c r="N48" s="3">
-        <v>13600</v>
+        <v>13500</v>
       </c>
       <c r="O48" s="3">
         <v>13600</v>
@@ -4471,10 +4578,10 @@
         <v>13600</v>
       </c>
       <c r="Q48" s="3">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
+        <v>13600</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
@@ -4488,8 +4595,8 @@
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
@@ -4530,8 +4637,11 @@
       <c r="AJ48" s="3">
         <v>0</v>
       </c>
+      <c r="AK48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4634,8 +4744,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4851,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,25 +4958,28 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+      <c r="H52" s="3">
+        <v>400</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
@@ -4874,8 +4993,8 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -4946,8 +5065,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,112 +5172,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E54" s="3">
         <v>158300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>93600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>66200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
+        <v>58600</v>
+      </c>
+      <c r="I54" s="3">
         <v>54900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>54900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>25700</v>
       </c>
-      <c r="J54" s="3">
-        <v>25700</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>36600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>14000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5320,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,89 +5359,90 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>300</v>
+      </c>
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
         <v>1200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>600</v>
       </c>
       <c r="N57" s="3">
         <v>600</v>
       </c>
       <c r="O57" s="3">
+        <v>600</v>
+      </c>
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>1900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
       <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
-      </c>
-      <c r="X57" s="3">
-        <v>100</v>
       </c>
       <c r="Y57" s="3">
         <v>100</v>
       </c>
       <c r="Z57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
-      </c>
       <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="3">
         <v>200</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
       <c r="AD57" s="3">
         <v>0</v>
       </c>
@@ -5323,45 +5453,48 @@
         <v>0</v>
       </c>
       <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
         <v>100</v>
       </c>
-      <c r="AH57" s="3">
-        <v>0</v>
-      </c>
       <c r="AI57" s="3">
         <v>0</v>
       </c>
       <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E58" s="3">
         <v>34900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>29900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I58" s="3">
         <v>2000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
@@ -5372,14 +5505,14 @@
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
-        <v>6300</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>6300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
+      <c r="Q58" s="3">
+        <v>6300</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
@@ -5396,8 +5529,8 @@
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -5438,25 +5571,28 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E59" s="3">
         <v>31000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9500</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
+      <c r="H59" s="3">
+        <v>2700</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
@@ -5464,53 +5600,53 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>1300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1000</v>
-      </c>
-      <c r="V59" s="3">
-        <v>200</v>
       </c>
       <c r="W59" s="3">
         <v>200</v>
       </c>
       <c r="X59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y59" s="3">
         <v>300</v>
       </c>
       <c r="Z59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AA59" s="3">
         <v>100</v>
@@ -5519,13 +5655,13 @@
         <v>100</v>
       </c>
       <c r="AC59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD59" s="3">
         <v>200</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
-      </c>
       <c r="AE59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF59" s="3">
         <v>100</v>
@@ -5540,93 +5676,96 @@
         <v>100</v>
       </c>
       <c r="AJ59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E60" s="3">
         <v>80500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>50500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
+        <v>13100</v>
+      </c>
+      <c r="I60" s="3">
         <v>5000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M60" s="3">
         <v>2300</v>
       </c>
-      <c r="K60" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P60" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>7200</v>
+      </c>
+      <c r="R60" s="3">
+        <v>200</v>
+      </c>
+      <c r="S60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T60" s="3">
         <v>2300</v>
       </c>
-      <c r="M60" s="3">
-        <v>1500</v>
-      </c>
-      <c r="N60" s="3">
-        <v>1200</v>
-      </c>
-      <c r="O60" s="3">
-        <v>6800</v>
-      </c>
-      <c r="P60" s="3">
-        <v>7200</v>
-      </c>
-      <c r="Q60" s="3">
+      <c r="U60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="V60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3">
-        <v>1200</v>
-      </c>
-      <c r="S60" s="3">
-        <v>2300</v>
-      </c>
-      <c r="T60" s="3">
-        <v>4300</v>
-      </c>
-      <c r="U60" s="3">
-        <v>1100</v>
-      </c>
-      <c r="V60" s="3">
-        <v>200</v>
-      </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>300</v>
-      </c>
-      <c r="X60" s="3">
-        <v>400</v>
       </c>
       <c r="Y60" s="3">
         <v>400</v>
       </c>
       <c r="Z60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA60" s="3">
         <v>200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>100</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>300</v>
       </c>
       <c r="AC60" s="3">
         <v>300</v>
       </c>
       <c r="AD60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AE60" s="3">
         <v>100</v>
@@ -5641,49 +5780,52 @@
         <v>100</v>
       </c>
       <c r="AI60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E61" s="3">
         <v>39000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>44700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>36800</v>
+      </c>
+      <c r="I61" s="3">
         <v>32900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>32900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>25500</v>
       </c>
-      <c r="J61" s="3">
-        <v>25500</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -5750,34 +5892,37 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E62" s="3">
         <v>46800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>36300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>32100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
+        <v>23300</v>
+      </c>
+      <c r="I62" s="3">
         <v>6000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>6000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K62" s="3">
-        <v>3300</v>
       </c>
       <c r="L62" s="3">
         <v>3300</v>
@@ -5795,7 +5940,7 @@
         <v>3300</v>
       </c>
       <c r="Q62" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="R62" s="3">
         <v>1200</v>
@@ -5806,8 +5951,8 @@
       <c r="T62" s="3">
         <v>1200</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
+      <c r="U62" s="3">
+        <v>1200</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
@@ -5824,8 +5969,8 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5854,8 +5999,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6106,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6213,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,91 +6320,94 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>132600</v>
+      </c>
+      <c r="E66" s="3">
         <v>168500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>131500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>100200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
+        <v>73100</v>
+      </c>
+      <c r="I66" s="3">
         <v>43800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>43800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>30400</v>
       </c>
-      <c r="J66" s="3">
-        <v>30400</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>300</v>
-      </c>
-      <c r="X66" s="3">
-        <v>400</v>
       </c>
       <c r="Y66" s="3">
         <v>400</v>
       </c>
       <c r="Z66" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA66" s="3">
         <v>200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>100</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>300</v>
       </c>
       <c r="AC66" s="3">
         <v>300</v>
       </c>
       <c r="AD66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AE66" s="3">
         <v>100</v>
@@ -6265,13 +6422,16 @@
         <v>100</v>
       </c>
       <c r="AI66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6468,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6573,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6680,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6620,8 +6787,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,112 +6894,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-177100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-187800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-178100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-159500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="I72" s="3">
         <v>-111400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-111400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-98300</v>
       </c>
-      <c r="J72" s="3">
-        <v>-98300</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-79900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-65600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-58500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-51300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-44500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-39600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-35000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-33200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-28700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-25500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-58900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-56300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-54400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-51500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-49700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-46100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-44200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-41300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-37500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-36600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-35800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-35100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-34300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-33800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-33200</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7108,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7215,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,112 +7322,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E76" s="3">
         <v>-10200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-37900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-34000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="I76" s="3">
         <v>11000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>11000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-4800</v>
       </c>
-      <c r="J76" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>31000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>34500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>28800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>31100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>16800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,221 +7536,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
-        <v>45107</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-20500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="I81" s="3">
         <v>-13100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-13100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-10400</v>
       </c>
-      <c r="J81" s="3">
-        <v>-10400</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>33400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,8 +7796,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7643,8 +7841,8 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
@@ -7661,8 +7859,8 @@
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -7703,8 +7901,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8008,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8115,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8222,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8329,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,112 +8436,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E89" s="3">
         <v>17500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-5300</v>
       </c>
       <c r="L89" s="3">
         <v>-5300</v>
       </c>
       <c r="M89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="N89" s="3">
         <v>-4700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-200</v>
       </c>
       <c r="Z89" s="3">
         <v>-200</v>
       </c>
       <c r="AA89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-300</v>
       </c>
       <c r="AD89" s="3">
         <v>-300</v>
       </c>
       <c r="AE89" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AF89" s="3">
         <v>-200</v>
       </c>
       <c r="AG89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,8 +8584,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8385,14 +8605,14 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8409,8 +8629,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
@@ -8427,8 +8647,8 @@
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -8469,8 +8689,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +8796,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,89 +8903,92 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="I94" s="3">
         <v>-27000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-27000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-6700</v>
       </c>
-      <c r="J94" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-7800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-2500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>31000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1800</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-900</v>
       </c>
       <c r="Y94" s="3">
         <v>-900</v>
       </c>
       <c r="Z94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>4</v>
       </c>
@@ -8772,8 +9001,8 @@
       <c r="AG94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH94" s="3">
-        <v>0</v>
+      <c r="AH94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI94" s="3">
         <v>0</v>
@@ -8781,8 +9010,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,8 +9051,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8845,8 +9078,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8923,8 +9156,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9263,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9370,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,67 +9477,70 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>30700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>10200</v>
+      </c>
+      <c r="I100" s="3">
         <v>37500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>37500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>16600</v>
       </c>
-      <c r="J100" s="3">
-        <v>16600</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>19800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>10900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-900</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>3200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>4</v>
@@ -9303,8 +9548,8 @@
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -9319,28 +9564,31 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>1100</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>4</v>
+      <c r="AI100" s="3">
+        <v>0</v>
       </c>
       <c r="AJ100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9365,8 +9613,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9443,108 +9691,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E102" s="3">
         <v>12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>16500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I102" s="3">
         <v>6900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>6900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>8700</v>
       </c>
-      <c r="J102" s="3">
-        <v>8700</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>33400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>10900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
   <si>
     <t>CTGO</t>
   </si>
@@ -656,157 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45199</v>
       </c>
       <c r="J7" s="2">
         <v>45199</v>
       </c>
       <c r="K7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -834,8 +838,8 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -912,8 +916,11 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1019,8 +1026,11 @@
       <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,8 +1136,11 @@
       <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1165,8 +1178,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1194,26 +1208,26 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3">
         <v>2300</v>
-      </c>
-      <c r="M12" s="3">
-        <v>4500</v>
       </c>
       <c r="N12" s="3">
         <v>4500</v>
       </c>
       <c r="O12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="P12" s="3">
         <v>2100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1100</v>
-      </c>
-      <c r="R12" s="3">
-        <v>100</v>
       </c>
       <c r="S12" s="3">
         <v>100</v>
@@ -1222,10 +1236,10 @@
         <v>100</v>
       </c>
       <c r="U12" s="3">
-        <v>0</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>4</v>
@@ -1272,8 +1286,11 @@
       <c r="AK12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1379,49 +1396,52 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
@@ -1438,8 +1458,8 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1486,8 +1506,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1533,8 +1556,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>4</v>
@@ -1551,8 +1574,8 @@
       <c r="W15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1593,8 +1616,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1629,222 +1655,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E17" s="3">
         <v>4500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4900</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4000</v>
       </c>
       <c r="J17" s="3">
         <v>4000</v>
       </c>
       <c r="K17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L17" s="3">
         <v>3700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>1100</v>
       </c>
       <c r="AB17" s="3">
         <v>1100</v>
       </c>
       <c r="AC17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD17" s="3">
         <v>1000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-4000</v>
       </c>
       <c r="J18" s="3">
         <v>-4000</v>
       </c>
       <c r="K18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="L18" s="3">
         <v>-3700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-1100</v>
       </c>
       <c r="AB18" s="3">
         <v>-1100</v>
       </c>
       <c r="AC18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1882,95 +1915,96 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-17300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>13200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>15800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>21300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>8300</v>
       </c>
       <c r="J20" s="3">
         <v>8300</v>
       </c>
       <c r="K20" s="3">
+        <v>8300</v>
+      </c>
+      <c r="L20" s="3">
         <v>6100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>39400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-900</v>
       </c>
       <c r="Z20" s="3">
         <v>-900</v>
       </c>
       <c r="AA20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
@@ -1989,56 +2023,59 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E21" s="3">
         <v>12800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-15600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-18500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-12300</v>
       </c>
       <c r="J21" s="3">
         <v>-12300</v>
       </c>
       <c r="K21" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="L21" s="3">
         <v>-9800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6600</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-6900</v>
       </c>
       <c r="O21" s="3">
         <v>-6900</v>
       </c>
       <c r="P21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2096,56 +2133,59 @@
       <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
         <v>3100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>800</v>
       </c>
       <c r="J22" s="3">
         <v>800</v>
       </c>
       <c r="K22" s="3">
+        <v>800</v>
+      </c>
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2161,8 +2201,8 @@
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -2203,127 +2243,133 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E23" s="3">
         <v>9900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-27600</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-13100</v>
       </c>
       <c r="J23" s="3">
         <v>-13100</v>
       </c>
       <c r="K23" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="L23" s="3">
         <v>-10400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>35800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2339,8 +2385,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2349,29 +2395,29 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2400</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2381,14 +2427,14 @@
       <c r="Y24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="Z24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2417,8 +2463,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2524,222 +2573,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E26" s="3">
         <v>10700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-27600</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-13100</v>
       </c>
       <c r="J26" s="3">
         <v>-13100</v>
       </c>
       <c r="K26" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="L26" s="3">
         <v>-10400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>33400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E27" s="3">
         <v>10700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-13100</v>
       </c>
       <c r="J27" s="3">
         <v>-13100</v>
       </c>
       <c r="K27" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="L27" s="3">
         <v>-10400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>33400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2845,8 +2903,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2952,8 +3013,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3059,8 +3123,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3166,95 +3233,98 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E32" s="3">
         <v>17300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-13200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-15800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-21300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-8300</v>
       </c>
       <c r="J32" s="3">
         <v>-8300</v>
       </c>
       <c r="K32" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-6100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-39400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1800</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>900</v>
       </c>
       <c r="Z32" s="3">
         <v>900</v>
       </c>
       <c r="AA32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB32" s="3">
         <v>400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2400</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
@@ -3273,115 +3343,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E33" s="3">
         <v>10700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-18500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-27600</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-13100</v>
       </c>
       <c r="J33" s="3">
         <v>-13100</v>
       </c>
       <c r="K33" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="L33" s="3">
         <v>-10400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>33400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3487,227 +3563,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E35" s="3">
         <v>10700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-18500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-27600</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-13100</v>
       </c>
       <c r="J35" s="3">
         <v>-13100</v>
       </c>
       <c r="K35" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="L35" s="3">
         <v>-10400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>33400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45199</v>
       </c>
       <c r="J38" s="2">
         <v>45199</v>
       </c>
       <c r="K38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3745,8 +3830,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3784,115 +3870,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E41" s="3">
         <v>20100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>24100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>18500</v>
       </c>
       <c r="J41" s="3">
         <v>18500</v>
       </c>
       <c r="K41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="L41" s="3">
         <v>11600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>21900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>26800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>35200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>26200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>31900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>36400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>16600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>15800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3998,16 +4088,19 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
+      <c r="E43" s="3">
+        <v>600</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>4</v>
@@ -4027,8 +4120,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4037,20 +4130,20 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>500</v>
-      </c>
-      <c r="P43" s="3">
-        <v>300</v>
       </c>
       <c r="Q43" s="3">
         <v>300</v>
       </c>
       <c r="R43" s="3">
+        <v>300</v>
+      </c>
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
@@ -4063,8 +4156,8 @@
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -4105,8 +4198,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4134,8 +4230,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4212,8 +4308,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4232,68 +4331,68 @@
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I45" s="3">
-        <v>500</v>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="K45" s="3">
+        <v>500</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>1000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>700</v>
       </c>
       <c r="N45" s="3">
         <v>700</v>
       </c>
       <c r="O45" s="3">
+        <v>700</v>
+      </c>
+      <c r="P45" s="3">
         <v>1500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
       <c r="Z45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
         <v>200</v>
       </c>
       <c r="AB45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC45" s="3">
         <v>100</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>200</v>
       </c>
       <c r="AD45" s="3">
         <v>200</v>
@@ -4302,161 +4401,167 @@
         <v>200</v>
       </c>
       <c r="AF45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG45" s="3">
         <v>100</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>200</v>
       </c>
       <c r="AH45" s="3">
         <v>200</v>
       </c>
       <c r="AI45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AJ45" s="3">
         <v>100</v>
       </c>
       <c r="AK45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E46" s="3">
         <v>22100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16900</v>
-      </c>
-      <c r="I46" s="3">
-        <v>20100</v>
       </c>
       <c r="J46" s="3">
         <v>20100</v>
       </c>
       <c r="K46" s="3">
+        <v>20100</v>
+      </c>
+      <c r="L46" s="3">
         <v>12300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>27800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>35900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>26800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>32400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>36600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>11800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E47" s="3">
         <v>61200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>68300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>54500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>28100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>21400</v>
       </c>
       <c r="J47" s="3">
         <v>21400</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3">
+        <v>21400</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4533,19 +4638,22 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E48" s="3">
         <v>50600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>52500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>13300</v>
       </c>
       <c r="G48" s="3">
         <v>13300</v>
@@ -4554,7 +4662,7 @@
         <v>13300</v>
       </c>
       <c r="I48" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="J48" s="3">
         <v>13400</v>
@@ -4566,13 +4674,13 @@
         <v>13400</v>
       </c>
       <c r="M48" s="3">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="N48" s="3">
         <v>13500</v>
       </c>
       <c r="O48" s="3">
-        <v>13600</v>
+        <v>13500</v>
       </c>
       <c r="P48" s="3">
         <v>13600</v>
@@ -4581,10 +4689,10 @@
         <v>13600</v>
       </c>
       <c r="R48" s="3">
-        <v>0</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>4</v>
+        <v>13600</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>4</v>
@@ -4598,8 +4706,8 @@
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -4640,8 +4748,11 @@
       <c r="AK48" s="3">
         <v>0</v>
       </c>
+      <c r="AL48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4747,8 +4858,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4854,8 +4968,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4961,28 +5078,31 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>400</v>
       </c>
       <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
+      <c r="I52" s="3">
+        <v>400</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
@@ -4996,8 +5116,8 @@
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -5068,8 +5188,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5175,115 +5298,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>147400</v>
+      </c>
+      <c r="E54" s="3">
         <v>133900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>158300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>93600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>66200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>58600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>54900</v>
       </c>
       <c r="J54" s="3">
         <v>54900</v>
       </c>
       <c r="K54" s="3">
+        <v>54900</v>
+      </c>
+      <c r="L54" s="3">
         <v>25700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>41500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>36000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>36600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>14000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5321,8 +5450,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5360,92 +5490,93 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2100</v>
       </c>
       <c r="J57" s="3">
         <v>2100</v>
       </c>
       <c r="K57" s="3">
-        <v>200</v>
+        <v>2100</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
       </c>
       <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
         <v>1200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>600</v>
       </c>
       <c r="O57" s="3">
         <v>600</v>
       </c>
       <c r="P57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
       <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
         <v>1900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
       <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
         <v>200</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>100</v>
       </c>
       <c r="Z57" s="3">
         <v>100</v>
       </c>
       <c r="AA57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
       <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="3">
         <v>200</v>
       </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
       <c r="AE57" s="3">
         <v>0</v>
       </c>
@@ -5456,48 +5587,51 @@
         <v>0</v>
       </c>
       <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3">
         <v>100</v>
       </c>
-      <c r="AI57" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
       <c r="AK57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E58" s="3">
         <v>42600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>34900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>29900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7900</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2000</v>
       </c>
       <c r="J58" s="3">
         <v>2000</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
+        <v>2000</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
@@ -5508,14 +5642,14 @@
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P58" s="3">
-        <v>6300</v>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q58" s="3">
         <v>6300</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
+      <c r="R58" s="3">
+        <v>6300</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
@@ -5532,8 +5666,8 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -5574,82 +5708,85 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E59" s="3">
         <v>29900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2700</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1000</v>
-      </c>
-      <c r="W59" s="3">
-        <v>200</v>
       </c>
       <c r="X59" s="3">
         <v>200</v>
       </c>
       <c r="Y59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z59" s="3">
         <v>300</v>
       </c>
       <c r="AA59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AB59" s="3">
         <v>100</v>
@@ -5658,13 +5795,13 @@
         <v>100</v>
       </c>
       <c r="AD59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE59" s="3">
         <v>200</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
-      </c>
       <c r="AF59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG59" s="3">
         <v>100</v>
@@ -5679,96 +5816,99 @@
         <v>100</v>
       </c>
       <c r="AK59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E60" s="3">
         <v>75800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>80500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>50500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>5000</v>
       </c>
       <c r="J60" s="3">
         <v>5000</v>
       </c>
       <c r="K60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L60" s="3">
         <v>2300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>300</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>400</v>
       </c>
       <c r="Z60" s="3">
         <v>400</v>
       </c>
       <c r="AA60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB60" s="3">
         <v>200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>100</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>300</v>
       </c>
       <c r="AD60" s="3">
         <v>300</v>
       </c>
       <c r="AE60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AF60" s="3">
         <v>100</v>
@@ -5783,52 +5923,55 @@
         <v>100</v>
       </c>
       <c r="AJ60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK60" s="3">
         <v>200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E61" s="3">
         <v>26400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>39000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>44700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>35400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36800</v>
-      </c>
-      <c r="I61" s="3">
-        <v>32900</v>
       </c>
       <c r="J61" s="3">
         <v>32900</v>
       </c>
       <c r="K61" s="3">
+        <v>32900</v>
+      </c>
+      <c r="L61" s="3">
         <v>25500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5895,37 +6038,40 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E62" s="3">
         <v>30200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>46800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>36300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>32100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>6000</v>
       </c>
       <c r="J62" s="3">
         <v>6000</v>
       </c>
       <c r="K62" s="3">
+        <v>6000</v>
+      </c>
+      <c r="L62" s="3">
         <v>2700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>3300</v>
       </c>
       <c r="M62" s="3">
         <v>3300</v>
@@ -5943,7 +6089,7 @@
         <v>3300</v>
       </c>
       <c r="R62" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="S62" s="3">
         <v>1200</v>
@@ -5954,8 +6100,8 @@
       <c r="U62" s="3">
         <v>1200</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
+      <c r="V62" s="3">
+        <v>1200</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
@@ -5972,8 +6118,8 @@
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -6002,8 +6148,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6109,8 +6258,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6216,8 +6368,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6323,94 +6478,97 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>167900</v>
+      </c>
+      <c r="E66" s="3">
         <v>132600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>168500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>131500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>73100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>43800</v>
       </c>
       <c r="J66" s="3">
         <v>43800</v>
       </c>
       <c r="K66" s="3">
+        <v>43800</v>
+      </c>
+      <c r="L66" s="3">
         <v>30400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>24000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>300</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>400</v>
       </c>
       <c r="Z66" s="3">
         <v>400</v>
       </c>
       <c r="AA66" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB66" s="3">
         <v>200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>100</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>300</v>
       </c>
       <c r="AD66" s="3">
         <v>300</v>
       </c>
       <c r="AE66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AF66" s="3">
         <v>100</v>
@@ -6425,13 +6583,16 @@
         <v>100</v>
       </c>
       <c r="AJ66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK66" s="3">
         <v>200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6469,8 +6630,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6576,8 +6738,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6683,8 +6848,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6790,8 +6958,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6897,115 +7068,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-199600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-177100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-187800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-178100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-159500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-139000</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-111400</v>
       </c>
       <c r="J72" s="3">
         <v>-111400</v>
       </c>
       <c r="K72" s="3">
+        <v>-111400</v>
+      </c>
+      <c r="L72" s="3">
         <v>-98300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-79900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-65600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-58500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-51300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-44500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-39600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-35000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-33200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-28700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-25500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-58900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-56300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-54400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-51500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-49700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-46100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-44200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-41300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-37500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-36600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-35800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-35100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-34300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-33800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-33200</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7111,8 +7288,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7218,8 +7398,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7325,115 +7508,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-10200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-37900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-34000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-14500</v>
-      </c>
-      <c r="I76" s="3">
-        <v>11000</v>
       </c>
       <c r="J76" s="3">
         <v>11000</v>
       </c>
       <c r="K76" s="3">
+        <v>11000</v>
+      </c>
+      <c r="L76" s="3">
         <v>-4800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>27300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>31000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>34500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>28800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>31100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>16800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7539,227 +7728,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45199</v>
       </c>
       <c r="J80" s="2">
         <v>45199</v>
       </c>
       <c r="K80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E81" s="3">
         <v>10700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-18500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-27600</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-13100</v>
       </c>
       <c r="J81" s="3">
         <v>-13100</v>
       </c>
       <c r="K81" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="L81" s="3">
         <v>-10400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>33400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7797,8 +7995,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7844,8 +8043,8 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>4</v>
@@ -7862,8 +8061,8 @@
       <c r="W83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -7904,8 +8103,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8011,8 +8213,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8118,8 +8323,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8225,8 +8433,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8332,8 +8543,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8439,115 +8653,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-3600</v>
       </c>
       <c r="J89" s="3">
         <v>-3600</v>
       </c>
       <c r="K89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="L89" s="3">
         <v>-1100</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-5300</v>
       </c>
       <c r="M89" s="3">
         <v>-5300</v>
       </c>
       <c r="N89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="O89" s="3">
         <v>-4700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-200</v>
       </c>
       <c r="AA89" s="3">
         <v>-200</v>
       </c>
       <c r="AB89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-300</v>
       </c>
       <c r="AE89" s="3">
         <v>-300</v>
       </c>
       <c r="AF89" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AG89" s="3">
         <v>-200</v>
       </c>
       <c r="AH89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8585,13 +8805,14 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -8611,11 +8832,11 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8632,8 +8853,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
@@ -8650,8 +8871,8 @@
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -8692,8 +8913,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8799,8 +9023,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8906,92 +9133,95 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7400</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-27000</v>
       </c>
       <c r="J94" s="3">
         <v>-27000</v>
       </c>
       <c r="K94" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="L94" s="3">
         <v>-6700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9300</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-7800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6600</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-2500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>31000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-900</v>
       </c>
       <c r="Z94" s="3">
         <v>-900</v>
       </c>
       <c r="AA94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>4</v>
       </c>
@@ -9004,8 +9234,8 @@
       <c r="AH94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI94" s="3">
-        <v>0</v>
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ94" s="3">
         <v>0</v>
@@ -9013,8 +9243,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9052,8 +9285,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9081,8 +9315,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9159,8 +9393,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9266,8 +9503,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9373,8 +9613,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9480,70 +9723,73 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>30700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>10200</v>
-      </c>
-      <c r="I100" s="3">
-        <v>37500</v>
       </c>
       <c r="J100" s="3">
         <v>37500</v>
       </c>
       <c r="K100" s="3">
+        <v>37500</v>
+      </c>
+      <c r="L100" s="3">
         <v>16600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5600</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>19800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>10900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>3200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>4</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>4</v>
@@ -9551,8 +9797,8 @@
       <c r="Y100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -9567,28 +9813,31 @@
         <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>1100</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
+      <c r="AH100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI100" s="3">
         <v>0</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>4</v>
+      <c r="AJ100" s="3">
+        <v>0</v>
       </c>
       <c r="AK100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9616,8 +9865,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9694,111 +9943,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I102" s="3">
-        <v>6900</v>
       </c>
       <c r="J102" s="3">
         <v>6900</v>
       </c>
       <c r="K102" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L102" s="3">
         <v>8700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>33400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>10900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>CTGO</t>
   </si>
@@ -656,161 +656,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45199</v>
       </c>
       <c r="K7" s="2">
         <v>45199</v>
       </c>
       <c r="L7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -841,8 +845,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -919,8 +923,11 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1029,8 +1036,11 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1149,11 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1179,8 +1192,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1211,26 +1225,26 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3">
         <v>2300</v>
-      </c>
-      <c r="N12" s="3">
-        <v>4500</v>
       </c>
       <c r="O12" s="3">
         <v>4500</v>
       </c>
       <c r="P12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Q12" s="3">
         <v>2100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1100</v>
-      </c>
-      <c r="S12" s="3">
-        <v>100</v>
       </c>
       <c r="T12" s="3">
         <v>100</v>
@@ -1239,10 +1253,10 @@
         <v>100</v>
       </c>
       <c r="V12" s="3">
-        <v>0</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>4</v>
@@ -1289,8 +1303,11 @@
       <c r="AL12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1399,52 +1416,55 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
@@ -1461,8 +1481,8 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1509,8 +1529,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1559,8 +1582,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>4</v>
@@ -1577,8 +1600,8 @@
       <c r="X15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1619,8 +1642,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1656,228 +1682,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E17" s="3">
         <v>3100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4900</v>
-      </c>
-      <c r="J17" s="3">
-        <v>4000</v>
       </c>
       <c r="K17" s="3">
         <v>4000</v>
       </c>
       <c r="L17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M17" s="3">
         <v>3700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1300</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>1100</v>
       </c>
       <c r="AC17" s="3">
         <v>1100</v>
       </c>
       <c r="AD17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE17" s="3">
         <v>1000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-4000</v>
       </c>
       <c r="K18" s="3">
         <v>-4000</v>
       </c>
       <c r="L18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="M18" s="3">
         <v>-3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-1100</v>
       </c>
       <c r="AC18" s="3">
         <v>-1100</v>
       </c>
       <c r="AD18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1916,98 +1949,99 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E20" s="3">
         <v>17000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-17300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>13200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>15800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>21300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>8300</v>
       </c>
       <c r="K20" s="3">
         <v>8300</v>
       </c>
       <c r="L20" s="3">
+        <v>8300</v>
+      </c>
+      <c r="M20" s="3">
         <v>6100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>39400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-900</v>
       </c>
       <c r="AA20" s="3">
         <v>-900</v>
       </c>
       <c r="AB20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
@@ -2026,59 +2060,62 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-15600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-18500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-12300</v>
       </c>
       <c r="K21" s="3">
         <v>-12300</v>
       </c>
       <c r="L21" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="M21" s="3">
         <v>-9800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-13800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6600</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-6900</v>
       </c>
       <c r="P21" s="3">
         <v>-6900</v>
       </c>
       <c r="Q21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="R21" s="3">
         <v>-4900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2136,59 +2173,62 @@
       <c r="AL21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>800</v>
       </c>
       <c r="K22" s="3">
         <v>800</v>
       </c>
       <c r="L22" s="3">
+        <v>800</v>
+      </c>
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2204,8 +2244,8 @@
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2246,133 +2286,139 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27600</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-13100</v>
       </c>
       <c r="K23" s="3">
         <v>-13100</v>
       </c>
       <c r="L23" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="M23" s="3">
         <v>-10400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>35800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2388,8 +2434,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2398,29 +2444,29 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2400</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2430,14 +2476,14 @@
       <c r="Z24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -2466,8 +2512,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2576,228 +2625,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-22500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-27600</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-13100</v>
       </c>
       <c r="K26" s="3">
         <v>-13100</v>
       </c>
       <c r="L26" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="M26" s="3">
         <v>-10400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>33400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-27600</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-13100</v>
       </c>
       <c r="K27" s="3">
         <v>-13100</v>
       </c>
       <c r="L27" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="M27" s="3">
         <v>-10400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>33400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2906,8 +2964,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3016,8 +3077,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3126,8 +3190,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3236,98 +3303,101 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-17000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>17300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-13200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-15800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-21300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-8300</v>
       </c>
       <c r="K32" s="3">
         <v>-8300</v>
       </c>
       <c r="L32" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="M32" s="3">
         <v>-6100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-39400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1800</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>900</v>
       </c>
       <c r="AA32" s="3">
         <v>900</v>
       </c>
       <c r="AB32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC32" s="3">
         <v>400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2400</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
@@ -3346,118 +3416,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27600</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-13100</v>
       </c>
       <c r="K33" s="3">
         <v>-13100</v>
       </c>
       <c r="L33" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="M33" s="3">
         <v>-10400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>33400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3566,233 +3642,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27600</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-13100</v>
       </c>
       <c r="K35" s="3">
         <v>-13100</v>
       </c>
       <c r="L35" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="M35" s="3">
         <v>-10400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>33400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45199</v>
       </c>
       <c r="K38" s="2">
         <v>45199</v>
       </c>
       <c r="L38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3831,8 +3916,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3871,118 +3957,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E41" s="3">
         <v>35000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>24100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15500</v>
-      </c>
-      <c r="J41" s="3">
-        <v>18500</v>
       </c>
       <c r="K41" s="3">
         <v>18500</v>
       </c>
       <c r="L41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="M41" s="3">
         <v>11600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>21900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>26800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>35200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>26200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>31900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>36400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>8600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>16600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>15800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4091,8 +4181,11 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4102,8 +4195,8 @@
       <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
+      <c r="F43" s="3">
+        <v>600</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
@@ -4123,8 +4216,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -4133,20 +4226,20 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>500</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>300</v>
       </c>
       <c r="R43" s="3">
         <v>300</v>
       </c>
       <c r="S43" s="3">
+        <v>300</v>
+      </c>
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
@@ -4159,8 +4252,8 @@
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -4201,13 +4294,16 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
+      <c r="D44" s="3">
+        <v>800</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>4</v>
@@ -4233,8 +4329,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4311,8 +4407,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4334,68 +4433,68 @@
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="3">
-        <v>500</v>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="L45" s="3">
+        <v>500</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>1000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>700</v>
       </c>
       <c r="O45" s="3">
         <v>700</v>
       </c>
       <c r="P45" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="3">
         <v>200</v>
       </c>
       <c r="AC45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD45" s="3">
         <v>100</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>200</v>
       </c>
       <c r="AE45" s="3">
         <v>200</v>
@@ -4404,167 +4503,173 @@
         <v>200</v>
       </c>
       <c r="AG45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH45" s="3">
         <v>100</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>200</v>
       </c>
       <c r="AI45" s="3">
         <v>200</v>
       </c>
       <c r="AJ45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AK45" s="3">
         <v>100</v>
       </c>
       <c r="AL45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E46" s="3">
         <v>37100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16900</v>
-      </c>
-      <c r="J46" s="3">
-        <v>20100</v>
       </c>
       <c r="K46" s="3">
         <v>20100</v>
       </c>
       <c r="L46" s="3">
+        <v>20100</v>
+      </c>
+      <c r="M46" s="3">
         <v>12300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>23700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>27800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>35900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>26800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>32400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>36600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>11800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E47" s="3">
         <v>59800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>61200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>68300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>54500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>43400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28100</v>
-      </c>
-      <c r="J47" s="3">
-        <v>21400</v>
       </c>
       <c r="K47" s="3">
         <v>21400</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="L47" s="3">
+        <v>21400</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4641,8 +4746,11 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4650,13 +4758,13 @@
         <v>50500</v>
       </c>
       <c r="E48" s="3">
+        <v>50500</v>
+      </c>
+      <c r="F48" s="3">
         <v>50600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>52500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>13300</v>
       </c>
       <c r="H48" s="3">
         <v>13300</v>
@@ -4665,7 +4773,7 @@
         <v>13300</v>
       </c>
       <c r="J48" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="K48" s="3">
         <v>13400</v>
@@ -4677,13 +4785,13 @@
         <v>13400</v>
       </c>
       <c r="N48" s="3">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="O48" s="3">
         <v>13500</v>
       </c>
       <c r="P48" s="3">
-        <v>13600</v>
+        <v>13500</v>
       </c>
       <c r="Q48" s="3">
         <v>13600</v>
@@ -4692,10 +4800,10 @@
         <v>13600</v>
       </c>
       <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
+        <v>13600</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>4</v>
@@ -4709,8 +4817,8 @@
       <c r="X48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -4751,8 +4859,11 @@
       <c r="AL48" s="3">
         <v>0</v>
       </c>
+      <c r="AM48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4861,8 +4972,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4971,8 +5085,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5081,8 +5198,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5092,20 +5212,20 @@
       <c r="E52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>400</v>
       </c>
       <c r="I52" s="3">
         <v>400</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3">
+        <v>400</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
@@ -5119,8 +5239,8 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -5191,8 +5311,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5301,118 +5424,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>153100</v>
+      </c>
+      <c r="E54" s="3">
         <v>147400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>133900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>158300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>93600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>58600</v>
-      </c>
-      <c r="J54" s="3">
-        <v>54900</v>
       </c>
       <c r="K54" s="3">
         <v>54900</v>
       </c>
       <c r="L54" s="3">
+        <v>54900</v>
+      </c>
+      <c r="M54" s="3">
         <v>25700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>41500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>36000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>36600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>14000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5451,8 +5580,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5491,95 +5621,96 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>8900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2100</v>
       </c>
       <c r="K57" s="3">
         <v>2100</v>
       </c>
       <c r="L57" s="3">
-        <v>200</v>
+        <v>2100</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
       </c>
       <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
         <v>1200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>600</v>
       </c>
       <c r="P57" s="3">
         <v>600</v>
       </c>
       <c r="Q57" s="3">
+        <v>600</v>
+      </c>
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
       <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
         <v>1900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
       <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
         <v>200</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>100</v>
       </c>
       <c r="AA57" s="3">
         <v>100</v>
       </c>
       <c r="AB57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC57" s="3">
         <v>200</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
       <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3">
         <v>200</v>
       </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
       <c r="AF57" s="3">
         <v>0</v>
       </c>
@@ -5590,51 +5721,54 @@
         <v>0</v>
       </c>
       <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>100</v>
       </c>
-      <c r="AJ57" s="3">
-        <v>0</v>
-      </c>
       <c r="AK57" s="3">
         <v>0</v>
       </c>
       <c r="AL57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E58" s="3">
         <v>24700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>42600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>34900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>29900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7900</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2000</v>
       </c>
       <c r="K58" s="3">
         <v>2000</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
+        <v>2000</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
@@ -5645,14 +5779,14 @@
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
-        <v>6300</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>6300</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
+      <c r="S58" s="3">
+        <v>6300</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
@@ -5669,8 +5803,8 @@
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5711,85 +5845,88 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E59" s="3">
         <v>55500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2700</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1000</v>
-      </c>
-      <c r="X59" s="3">
-        <v>200</v>
       </c>
       <c r="Y59" s="3">
         <v>200</v>
       </c>
       <c r="Z59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AA59" s="3">
         <v>300</v>
       </c>
       <c r="AB59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AC59" s="3">
         <v>100</v>
@@ -5798,13 +5935,13 @@
         <v>100</v>
       </c>
       <c r="AE59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF59" s="3">
         <v>200</v>
       </c>
-      <c r="AF59" s="3">
-        <v>0</v>
-      </c>
       <c r="AG59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH59" s="3">
         <v>100</v>
@@ -5819,99 +5956,102 @@
         <v>100</v>
       </c>
       <c r="AL59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E60" s="3">
         <v>91000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>75800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>80500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>50500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>5000</v>
       </c>
       <c r="K60" s="3">
         <v>5000</v>
       </c>
       <c r="L60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="M60" s="3">
         <v>2300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>300</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>400</v>
       </c>
       <c r="AA60" s="3">
         <v>400</v>
       </c>
       <c r="AB60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC60" s="3">
         <v>200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>100</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>300</v>
       </c>
       <c r="AE60" s="3">
         <v>300</v>
       </c>
       <c r="AF60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AG60" s="3">
         <v>100</v>
@@ -5926,55 +6066,58 @@
         <v>100</v>
       </c>
       <c r="AK60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL60" s="3">
         <v>200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E61" s="3">
         <v>31400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>44700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>35400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36800</v>
-      </c>
-      <c r="J61" s="3">
-        <v>32900</v>
       </c>
       <c r="K61" s="3">
         <v>32900</v>
       </c>
       <c r="L61" s="3">
+        <v>32900</v>
+      </c>
+      <c r="M61" s="3">
         <v>25500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6041,40 +6184,43 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E62" s="3">
         <v>45000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>30200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>46800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>36300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>32100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>6000</v>
       </c>
       <c r="K62" s="3">
         <v>6000</v>
       </c>
       <c r="L62" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M62" s="3">
         <v>2700</v>
-      </c>
-      <c r="M62" s="3">
-        <v>3300</v>
       </c>
       <c r="N62" s="3">
         <v>3300</v>
@@ -6092,7 +6238,7 @@
         <v>3300</v>
       </c>
       <c r="S62" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="T62" s="3">
         <v>1200</v>
@@ -6103,8 +6249,8 @@
       <c r="V62" s="3">
         <v>1200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
+      <c r="W62" s="3">
+        <v>1200</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>4</v>
@@ -6121,8 +6267,8 @@
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -6151,8 +6297,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6261,8 +6410,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6371,8 +6523,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6481,97 +6636,100 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>155500</v>
+      </c>
+      <c r="E66" s="3">
         <v>167900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>132600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>168500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>131500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>100200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>73100</v>
-      </c>
-      <c r="J66" s="3">
-        <v>43800</v>
       </c>
       <c r="K66" s="3">
         <v>43800</v>
       </c>
       <c r="L66" s="3">
+        <v>43800</v>
+      </c>
+      <c r="M66" s="3">
         <v>30400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>24900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>300</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>400</v>
       </c>
       <c r="AA66" s="3">
         <v>400</v>
       </c>
       <c r="AB66" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC66" s="3">
         <v>200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>100</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>300</v>
       </c>
       <c r="AE66" s="3">
         <v>300</v>
       </c>
       <c r="AF66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AG66" s="3">
         <v>100</v>
@@ -6586,13 +6744,16 @@
         <v>100</v>
       </c>
       <c r="AK66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL66" s="3">
         <v>200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6631,8 +6792,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6741,8 +6903,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6851,8 +7016,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6961,8 +7129,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7071,118 +7242,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-183700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-199600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-177100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-187800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-178100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-159500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-139000</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-111400</v>
       </c>
       <c r="K72" s="3">
         <v>-111400</v>
       </c>
       <c r="L72" s="3">
+        <v>-111400</v>
+      </c>
+      <c r="M72" s="3">
         <v>-98300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-79900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-65600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-58500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-51300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-44500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-39600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-35000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-33200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-28700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-25500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-58900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-56300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-54400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-51500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-49700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-46100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-44200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-41300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-37500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-36600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-35800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-35100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-34300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-33800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-33200</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7291,8 +7468,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7401,8 +7581,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7511,118 +7694,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-20500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-10200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-37900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-34000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-14500</v>
-      </c>
-      <c r="J76" s="3">
-        <v>11000</v>
       </c>
       <c r="K76" s="3">
         <v>11000</v>
       </c>
       <c r="L76" s="3">
+        <v>11000</v>
+      </c>
+      <c r="M76" s="3">
         <v>-4800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>27300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>31000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>34500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>28800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>31100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>16800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7731,233 +7920,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45199</v>
       </c>
       <c r="K80" s="2">
         <v>45199</v>
       </c>
       <c r="L80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27600</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-13100</v>
       </c>
       <c r="K81" s="3">
         <v>-13100</v>
       </c>
       <c r="L81" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="M81" s="3">
         <v>-10400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>33400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7996,8 +8194,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8046,8 +8245,8 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>4</v>
@@ -8064,8 +8263,8 @@
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -8106,8 +8305,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8216,8 +8418,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8326,8 +8531,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8436,8 +8644,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8546,8 +8757,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8656,118 +8870,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E89" s="3">
         <v>28600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5900</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-3600</v>
       </c>
       <c r="K89" s="3">
         <v>-3600</v>
       </c>
       <c r="L89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="M89" s="3">
         <v>-1100</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-5300</v>
       </c>
       <c r="N89" s="3">
         <v>-5300</v>
       </c>
       <c r="O89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="P89" s="3">
         <v>-4700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-200</v>
       </c>
       <c r="AB89" s="3">
         <v>-200</v>
       </c>
       <c r="AC89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-300</v>
       </c>
       <c r="AF89" s="3">
         <v>-300</v>
       </c>
       <c r="AG89" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AH89" s="3">
         <v>-200</v>
       </c>
       <c r="AI89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8806,16 +9026,17 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -8835,11 +9056,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8856,8 +9077,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
@@ -8874,8 +9095,8 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -8916,8 +9137,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9026,8 +9250,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9136,95 +9363,98 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
         <v>-200</v>
       </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="F94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-4700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7400</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-27000</v>
       </c>
       <c r="K94" s="3">
         <v>-27000</v>
       </c>
       <c r="L94" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="M94" s="3">
         <v>-6700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6600</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-2500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>31000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-900</v>
       </c>
       <c r="AA94" s="3">
         <v>-900</v>
       </c>
       <c r="AB94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
@@ -9237,8 +9467,8 @@
       <c r="AI94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ94" s="3">
-        <v>0</v>
+      <c r="AJ94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK94" s="3">
         <v>0</v>
@@ -9246,8 +9476,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9286,8 +9519,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9318,8 +9552,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9396,8 +9630,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9506,8 +9743,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9616,8 +9856,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9726,73 +9969,76 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>30700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>10200</v>
-      </c>
-      <c r="J100" s="3">
-        <v>37500</v>
       </c>
       <c r="K100" s="3">
         <v>37500</v>
       </c>
       <c r="L100" s="3">
+        <v>37500</v>
+      </c>
+      <c r="M100" s="3">
         <v>16600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5600</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>19800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>10900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>3200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>4</v>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>4</v>
@@ -9800,8 +10046,8 @@
       <c r="Z100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
@@ -9816,28 +10062,31 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>1100</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI100" s="3">
-        <v>0</v>
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>4</v>
+      <c r="AK100" s="3">
+        <v>0</v>
       </c>
       <c r="AL100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9868,8 +10117,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9946,114 +10195,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E102" s="3">
         <v>14900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3000</v>
-      </c>
-      <c r="J102" s="3">
-        <v>6900</v>
       </c>
       <c r="K102" s="3">
         <v>6900</v>
       </c>
       <c r="L102" s="3">
+        <v>6900</v>
+      </c>
+      <c r="M102" s="3">
         <v>8700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>33400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>10900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>4700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="92">
   <si>
     <t>CTGO</t>
   </si>
@@ -656,169 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45199</v>
       </c>
       <c r="M7" s="2">
         <v>45199</v>
       </c>
       <c r="N7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -855,8 +858,8 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -933,8 +936,11 @@
       <c r="AN8" s="3">
         <v>0</v>
       </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1049,8 +1055,11 @@
       <c r="AN9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1165,8 +1174,11 @@
       <c r="AN10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1245,26 +1258,26 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3">
         <v>2300</v>
-      </c>
-      <c r="P12" s="3">
-        <v>4500</v>
       </c>
       <c r="Q12" s="3">
         <v>4500</v>
       </c>
       <c r="R12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="S12" s="3">
         <v>2100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1100</v>
-      </c>
-      <c r="U12" s="3">
-        <v>100</v>
       </c>
       <c r="V12" s="3">
         <v>100</v>
@@ -1273,10 +1286,10 @@
         <v>100</v>
       </c>
       <c r="X12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>4</v>
@@ -1323,8 +1336,11 @@
       <c r="AN12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1439,8 +1455,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1448,49 +1467,49 @@
         <v>1000</v>
       </c>
       <c r="E14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="3">
         <v>-6400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
@@ -1507,8 +1526,8 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1555,13 +1574,16 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1611,8 +1633,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>4</v>
@@ -1629,8 +1651,8 @@
       <c r="Z15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1671,8 +1693,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,240 +1735,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E17" s="3">
         <v>4600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4900</v>
-      </c>
-      <c r="L17" s="3">
-        <v>4000</v>
       </c>
       <c r="M17" s="3">
         <v>4000</v>
       </c>
       <c r="N17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O17" s="3">
         <v>3700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1300</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>1100</v>
       </c>
       <c r="AE17" s="3">
         <v>1100</v>
       </c>
       <c r="AF17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG17" s="3">
         <v>1000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-4000</v>
       </c>
       <c r="M18" s="3">
         <v>-4000</v>
       </c>
       <c r="N18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="O18" s="3">
         <v>-3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-1100</v>
       </c>
       <c r="AE18" s="3">
         <v>-1100</v>
       </c>
       <c r="AF18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1984,104 +2016,105 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-15400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>17000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-17300</v>
-      </c>
       <c r="H20" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>13200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>15800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>21300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>8300</v>
       </c>
       <c r="M20" s="3">
         <v>8300</v>
       </c>
       <c r="N20" s="3">
+        <v>8300</v>
+      </c>
+      <c r="O20" s="3">
         <v>6100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>39400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-900</v>
       </c>
       <c r="AC20" s="3">
         <v>-900</v>
       </c>
       <c r="AD20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
@@ -2100,65 +2133,68 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20000</v>
       </c>
-      <c r="G21" s="3">
-        <v>12800</v>
-      </c>
       <c r="H21" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-5200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-18500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26100</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-12300</v>
       </c>
       <c r="M21" s="3">
         <v>-12300</v>
       </c>
       <c r="N21" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="O21" s="3">
         <v>-9800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-13800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6600</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-6900</v>
       </c>
       <c r="R21" s="3">
         <v>-6900</v>
       </c>
       <c r="S21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="T21" s="3">
         <v>-4900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2216,65 +2252,68 @@
       <c r="AN21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="3">
         <v>1700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>800</v>
       </c>
       <c r="M22" s="3">
         <v>800</v>
       </c>
       <c r="N22" s="3">
+        <v>800</v>
+      </c>
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2290,8 +2329,8 @@
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -2332,145 +2371,151 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-22300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27600</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-13100</v>
       </c>
       <c r="M23" s="3">
         <v>-13100</v>
       </c>
       <c r="N23" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="O23" s="3">
         <v>-10400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>35800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>-100</v>
       </c>
       <c r="F24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2486,8 +2531,8 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2496,29 +2541,29 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2400</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2528,14 +2573,14 @@
       <c r="AB24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>0</v>
+      <c r="AC24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF24" s="3">
         <v>0</v>
@@ -2564,8 +2609,11 @@
       <c r="AN24" s="3">
         <v>0</v>
       </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2680,240 +2728,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-22500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-18500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-20500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27600</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-13100</v>
       </c>
       <c r="M26" s="3">
         <v>-13100</v>
       </c>
       <c r="N26" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="O26" s="3">
         <v>-10400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>33400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-22500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-18500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-27600</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-13100</v>
       </c>
       <c r="M27" s="3">
         <v>-13100</v>
       </c>
       <c r="N27" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="O27" s="3">
         <v>-10400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>33400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3028,8 +3085,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3144,8 +3204,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3260,8 +3323,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3376,104 +3442,107 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>15400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-17000</v>
       </c>
-      <c r="G32" s="3">
-        <v>17300</v>
-      </c>
       <c r="H32" s="3">
+        <v>17200</v>
+      </c>
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-13200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-15800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-21300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-8300</v>
       </c>
       <c r="M32" s="3">
         <v>-8300</v>
       </c>
       <c r="N32" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="O32" s="3">
         <v>-6100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-39400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1800</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>900</v>
       </c>
       <c r="AC32" s="3">
         <v>900</v>
       </c>
       <c r="AD32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE32" s="3">
         <v>400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2400</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
@@ -3492,124 +3561,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-22500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-18500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27600</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-13100</v>
       </c>
       <c r="M33" s="3">
         <v>-13100</v>
       </c>
       <c r="N33" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="O33" s="3">
         <v>-10400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>33400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3724,245 +3799,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-22500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-18500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27600</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-13100</v>
       </c>
       <c r="M35" s="3">
         <v>-13100</v>
       </c>
       <c r="N35" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="O35" s="3">
         <v>-10400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>33400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45199</v>
       </c>
       <c r="M38" s="2">
         <v>45199</v>
       </c>
       <c r="N38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4003,8 +4087,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4045,124 +4130,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E41" s="3">
         <v>107000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>35000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15500</v>
-      </c>
-      <c r="L41" s="3">
-        <v>18500</v>
       </c>
       <c r="M41" s="3">
         <v>18500</v>
       </c>
       <c r="N41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="O41" s="3">
         <v>11600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>23100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>26800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>35200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>26200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>31900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>36400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>8600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>16600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>15800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>5800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4277,8 +4366,11 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4286,7 +4378,7 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>600</v>
@@ -4294,8 +4386,8 @@
       <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
+      <c r="H43" s="3">
+        <v>600</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
@@ -4315,8 +4407,8 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -4325,20 +4417,20 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>500</v>
-      </c>
-      <c r="S43" s="3">
-        <v>300</v>
       </c>
       <c r="T43" s="3">
         <v>300</v>
       </c>
       <c r="U43" s="3">
+        <v>300</v>
+      </c>
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
@@ -4351,8 +4443,8 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -4393,20 +4485,23 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>800</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
@@ -4431,8 +4526,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4509,8 +4604,11 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4538,68 +4636,68 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
-        <v>500</v>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="N45" s="3">
+        <v>500</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>1000</v>
-      </c>
-      <c r="P45" s="3">
-        <v>700</v>
       </c>
       <c r="Q45" s="3">
         <v>700</v>
       </c>
       <c r="R45" s="3">
+        <v>700</v>
+      </c>
+      <c r="S45" s="3">
         <v>1500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
       <c r="AC45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="3">
         <v>200</v>
       </c>
       <c r="AE45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF45" s="3">
         <v>100</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>200</v>
       </c>
       <c r="AG45" s="3">
         <v>200</v>
@@ -4608,179 +4706,185 @@
         <v>200</v>
       </c>
       <c r="AI45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>100</v>
-      </c>
-      <c r="AJ45" s="3">
-        <v>200</v>
       </c>
       <c r="AK45" s="3">
         <v>200</v>
       </c>
       <c r="AL45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AM45" s="3">
         <v>100</v>
       </c>
       <c r="AN45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>68300</v>
+      </c>
+      <c r="E46" s="3">
         <v>108100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>38900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16900</v>
-      </c>
-      <c r="L46" s="3">
-        <v>20100</v>
       </c>
       <c r="M46" s="3">
         <v>20100</v>
       </c>
       <c r="N46" s="3">
+        <v>20100</v>
+      </c>
+      <c r="O46" s="3">
         <v>12300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>23800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>23700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>27800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>35900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>26800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>32400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>36600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>11800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>16800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>15900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E47" s="3">
         <v>59200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>63800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>61200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>68300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>54500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28100</v>
-      </c>
-      <c r="L47" s="3">
-        <v>21400</v>
       </c>
       <c r="M47" s="3">
         <v>21400</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="N47" s="3">
+        <v>21400</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4857,28 +4961,31 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E48" s="3">
         <v>50400</v>
-      </c>
-      <c r="E48" s="3">
-        <v>50500</v>
       </c>
       <c r="F48" s="3">
         <v>50500</v>
       </c>
       <c r="G48" s="3">
+        <v>50500</v>
+      </c>
+      <c r="H48" s="3">
         <v>50600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>52500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>13300</v>
       </c>
       <c r="J48" s="3">
         <v>13300</v>
@@ -4887,7 +4994,7 @@
         <v>13300</v>
       </c>
       <c r="L48" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="M48" s="3">
         <v>13400</v>
@@ -4899,13 +5006,13 @@
         <v>13400</v>
       </c>
       <c r="P48" s="3">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="Q48" s="3">
         <v>13500</v>
       </c>
       <c r="R48" s="3">
-        <v>13600</v>
+        <v>13500</v>
       </c>
       <c r="S48" s="3">
         <v>13600</v>
@@ -4914,10 +5021,10 @@
         <v>13600</v>
       </c>
       <c r="U48" s="3">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>4</v>
+        <v>13600</v>
+      </c>
+      <c r="V48" s="3">
+        <v>0</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>4</v>
@@ -4931,8 +5038,8 @@
       <c r="Z48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -4973,8 +5080,11 @@
       <c r="AN48" s="3">
         <v>0</v>
       </c>
+      <c r="AO48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5089,8 +5199,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5205,8 +5318,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5321,8 +5437,11 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5338,20 +5457,20 @@
       <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>400</v>
       </c>
       <c r="K52" s="3">
         <v>400</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
+      <c r="L52" s="3">
+        <v>400</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
@@ -5365,8 +5484,8 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -5437,8 +5556,11 @@
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5553,124 +5675,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E54" s="3">
         <v>217700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>153100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>147400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>133900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>158300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>93600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>66200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>58600</v>
-      </c>
-      <c r="L54" s="3">
-        <v>54900</v>
       </c>
       <c r="M54" s="3">
         <v>54900</v>
       </c>
       <c r="N54" s="3">
+        <v>54900</v>
+      </c>
+      <c r="O54" s="3">
         <v>25700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>23600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>37400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>41500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>36000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>36600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>14000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>16800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5711,8 +5839,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5753,101 +5882,102 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>9500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2100</v>
       </c>
       <c r="M57" s="3">
         <v>2100</v>
       </c>
       <c r="N57" s="3">
-        <v>200</v>
+        <v>2100</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
       </c>
       <c r="P57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>600</v>
       </c>
       <c r="R57" s="3">
         <v>600</v>
       </c>
       <c r="S57" s="3">
+        <v>600</v>
+      </c>
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
       <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
       <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
         <v>1900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>100</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
       <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
         <v>200</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>100</v>
       </c>
       <c r="AC57" s="3">
         <v>100</v>
       </c>
       <c r="AD57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE57" s="3">
         <v>200</v>
       </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
       <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
         <v>200</v>
       </c>
-      <c r="AG57" s="3">
-        <v>0</v>
-      </c>
       <c r="AH57" s="3">
         <v>0</v>
       </c>
@@ -5858,57 +5988,60 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="3">
         <v>100</v>
       </c>
-      <c r="AL57" s="3">
-        <v>0</v>
-      </c>
       <c r="AM57" s="3">
         <v>0</v>
       </c>
       <c r="AN57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>24700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>42600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>34900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>29900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7900</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2000</v>
       </c>
       <c r="M58" s="3">
         <v>2000</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
+        <v>2000</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
@@ -5919,14 +6052,14 @@
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S58" s="3">
-        <v>6300</v>
+      <c r="S58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T58" s="3">
         <v>6300</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
+      <c r="U58" s="3">
+        <v>6300</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
@@ -5943,8 +6076,8 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5985,91 +6118,94 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E59" s="3">
         <v>73000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>60600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>55500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>31000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2700</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>1300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>200</v>
       </c>
       <c r="AA59" s="3">
         <v>200</v>
       </c>
       <c r="AB59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC59" s="3">
         <v>300</v>
       </c>
       <c r="AD59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AE59" s="3">
         <v>100</v>
@@ -6078,13 +6214,13 @@
         <v>100</v>
       </c>
       <c r="AG59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH59" s="3">
         <v>200</v>
       </c>
-      <c r="AH59" s="3">
-        <v>0</v>
-      </c>
       <c r="AI59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ59" s="3">
         <v>100</v>
@@ -6099,105 +6235,108 @@
         <v>100</v>
       </c>
       <c r="AN59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E60" s="3">
         <v>95200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>82100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>91000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>75800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>80500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>50500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13100</v>
-      </c>
-      <c r="L60" s="3">
-        <v>5000</v>
       </c>
       <c r="M60" s="3">
         <v>5000</v>
       </c>
       <c r="N60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O60" s="3">
         <v>2300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>300</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>400</v>
       </c>
       <c r="AC60" s="3">
         <v>400</v>
       </c>
       <c r="AD60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE60" s="3">
         <v>200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>100</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>300</v>
       </c>
       <c r="AG60" s="3">
         <v>300</v>
       </c>
       <c r="AH60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AI60" s="3">
         <v>100</v>
@@ -6212,61 +6351,64 @@
         <v>100</v>
       </c>
       <c r="AM60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN60" s="3">
         <v>200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E61" s="3">
         <v>30600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>31000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>39000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>44700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>35400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>36800</v>
-      </c>
-      <c r="L61" s="3">
-        <v>32900</v>
       </c>
       <c r="M61" s="3">
         <v>32900</v>
       </c>
       <c r="N61" s="3">
+        <v>32900</v>
+      </c>
+      <c r="O61" s="3">
         <v>25500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>19200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -6333,46 +6475,49 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E62" s="3">
         <v>43700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>41900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>45000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>30200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>46800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>32100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23300</v>
-      </c>
-      <c r="L62" s="3">
-        <v>6000</v>
       </c>
       <c r="M62" s="3">
         <v>6000</v>
       </c>
       <c r="N62" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O62" s="3">
         <v>2700</v>
-      </c>
-      <c r="O62" s="3">
-        <v>3300</v>
       </c>
       <c r="P62" s="3">
         <v>3300</v>
@@ -6390,7 +6535,7 @@
         <v>3300</v>
       </c>
       <c r="U62" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="V62" s="3">
         <v>1200</v>
@@ -6401,8 +6546,8 @@
       <c r="X62" s="3">
         <v>1200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
+      <c r="Y62" s="3">
+        <v>1200</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>4</v>
@@ -6419,8 +6564,8 @@
       <c r="AD62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -6449,8 +6594,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6565,8 +6713,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6681,8 +6832,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6797,103 +6951,106 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>146900</v>
+      </c>
+      <c r="E66" s="3">
         <v>169800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>155500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>167900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>132600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>168500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>131500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73100</v>
-      </c>
-      <c r="L66" s="3">
-        <v>43800</v>
       </c>
       <c r="M66" s="3">
         <v>43800</v>
       </c>
       <c r="N66" s="3">
+        <v>43800</v>
+      </c>
+      <c r="O66" s="3">
         <v>30400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>24000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>300</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>400</v>
       </c>
       <c r="AC66" s="3">
         <v>400</v>
       </c>
       <c r="AD66" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE66" s="3">
         <v>200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>100</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>300</v>
       </c>
       <c r="AG66" s="3">
         <v>300</v>
       </c>
       <c r="AH66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AI66" s="3">
         <v>100</v>
@@ -6908,13 +7065,16 @@
         <v>100</v>
       </c>
       <c r="AM66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN66" s="3">
         <v>200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6955,8 +7115,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7071,8 +7232,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7187,8 +7351,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7303,8 +7470,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7419,124 +7589,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-213200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-189100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-183700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-199600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-177100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-187800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-178100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-159500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-139000</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-111400</v>
       </c>
       <c r="M72" s="3">
         <v>-111400</v>
       </c>
       <c r="N72" s="3">
+        <v>-111400</v>
+      </c>
+      <c r="O72" s="3">
         <v>-98300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-79900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-65600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-58500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-51300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-44500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-39600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-35000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-33200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-28700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-25500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-58900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-54400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-51500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-49700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-46100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-44200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-41300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-37500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-36600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-35800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-35100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-34300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-33800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-33200</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7651,8 +7827,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7767,8 +7946,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7883,124 +8065,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E76" s="3">
         <v>47800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-20500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-10200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-37900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-34000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-14500</v>
-      </c>
-      <c r="L76" s="3">
-        <v>11000</v>
       </c>
       <c r="M76" s="3">
         <v>11000</v>
       </c>
       <c r="N76" s="3">
+        <v>11000</v>
+      </c>
+      <c r="O76" s="3">
         <v>-4800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>27300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>31000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>34500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>24400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>28800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>31100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>16800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8115,245 +8303,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45199</v>
       </c>
       <c r="M80" s="2">
         <v>45199</v>
       </c>
       <c r="N80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-22500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-18500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27600</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-13100</v>
       </c>
       <c r="M81" s="3">
         <v>-13100</v>
       </c>
       <c r="N81" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="O81" s="3">
         <v>-10400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>33400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8394,8 +8591,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8450,8 +8648,8 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>4</v>
@@ -8468,8 +8666,8 @@
       <c r="Z83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -8510,8 +8708,11 @@
       <c r="AN83" s="3">
         <v>0</v>
       </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8626,8 +8827,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8742,8 +8946,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8858,8 +9065,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8974,8 +9184,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9090,124 +9303,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="E89" s="3">
         <v>23300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>28600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5900</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-3600</v>
       </c>
       <c r="M89" s="3">
         <v>-3600</v>
       </c>
       <c r="N89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="O89" s="3">
         <v>-1100</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-5300</v>
       </c>
       <c r="P89" s="3">
         <v>-5300</v>
       </c>
       <c r="Q89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="R89" s="3">
         <v>-4700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-100</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-200</v>
       </c>
       <c r="AD89" s="3">
         <v>-200</v>
       </c>
       <c r="AE89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>-300</v>
       </c>
       <c r="AH89" s="3">
         <v>-300</v>
       </c>
       <c r="AI89" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AJ89" s="3">
         <v>-200</v>
       </c>
       <c r="AK89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AL89" s="3">
         <v>-400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9248,22 +9467,23 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -9283,11 +9503,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -9304,8 +9524,8 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
@@ -9322,8 +9542,8 @@
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -9364,8 +9584,11 @@
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9480,8 +9703,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9596,101 +9822,104 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-200</v>
+        <v>900</v>
       </c>
       <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="H94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I94" s="3">
         <v>-4700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7400</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-27000</v>
       </c>
       <c r="M94" s="3">
         <v>-27000</v>
       </c>
       <c r="N94" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="O94" s="3">
         <v>-6700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-7800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6600</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-2500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>31000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-900</v>
       </c>
       <c r="AC94" s="3">
         <v>-900</v>
       </c>
       <c r="AD94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>4</v>
       </c>
@@ -9703,8 +9932,8 @@
       <c r="AK94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AL94" s="3">
-        <v>0</v>
+      <c r="AL94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AM94" s="3">
         <v>0</v>
@@ -9712,8 +9941,11 @@
       <c r="AN94" s="3">
         <v>0</v>
       </c>
+      <c r="AO94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9754,8 +9986,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9792,8 +10025,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9870,8 +10103,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9986,8 +10222,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10102,8 +10341,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10218,79 +10460,82 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E100" s="3">
         <v>47500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>30700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>10200</v>
-      </c>
-      <c r="L100" s="3">
-        <v>37500</v>
       </c>
       <c r="M100" s="3">
         <v>37500</v>
       </c>
       <c r="N100" s="3">
+        <v>37500</v>
+      </c>
+      <c r="O100" s="3">
         <v>16600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5600</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>19800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>10900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>3200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>4</v>
@@ -10298,8 +10543,8 @@
       <c r="AB100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
@@ -10314,28 +10559,31 @@
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>1100</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK100" s="3">
-        <v>0</v>
+      <c r="AK100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL100" s="3">
         <v>0</v>
       </c>
-      <c r="AM100" s="3" t="s">
-        <v>4</v>
+      <c r="AM100" s="3">
+        <v>0</v>
       </c>
       <c r="AN100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10372,8 +10620,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10450,120 +10698,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="E102" s="3">
         <v>70500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
-      </c>
-      <c r="L102" s="3">
-        <v>6900</v>
       </c>
       <c r="M102" s="3">
         <v>6900</v>
       </c>
       <c r="N102" s="3">
+        <v>6900</v>
+      </c>
+      <c r="O102" s="3">
         <v>8700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>33400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>4700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>CTGO</t>
   </si>
@@ -656,172 +656,176 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
-      </c>
-      <c r="M7" s="2">
-        <v>45199</v>
       </c>
       <c r="N7" s="2">
         <v>45199</v>
       </c>
       <c r="O7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -861,8 +865,8 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -939,8 +943,11 @@
       <c r="AO8" s="3">
         <v>0</v>
       </c>
+      <c r="AP8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1058,8 +1065,11 @@
       <c r="AO9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1177,8 +1187,11 @@
       <c r="AO10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1220,8 +1233,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1261,26 +1275,26 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3">
         <v>2300</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>4500</v>
       </c>
       <c r="R12" s="3">
         <v>4500</v>
       </c>
       <c r="S12" s="3">
+        <v>4500</v>
+      </c>
+      <c r="T12" s="3">
         <v>2100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1100</v>
-      </c>
-      <c r="V12" s="3">
-        <v>100</v>
       </c>
       <c r="W12" s="3">
         <v>100</v>
@@ -1289,10 +1303,10 @@
         <v>100</v>
       </c>
       <c r="Y12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>0</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>4</v>
@@ -1339,8 +1353,11 @@
       <c r="AO12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1458,61 +1475,64 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E14" s="3">
         <v>1000</v>
       </c>
       <c r="F14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-6400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
@@ -1529,8 +1549,8 @@
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1577,17 +1597,20 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
@@ -1636,8 +1659,8 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>4</v>
@@ -1654,8 +1677,8 @@
       <c r="AA15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1696,8 +1719,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,246 +1762,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E17" s="3">
         <v>7600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4300</v>
       </c>
-      <c r="G17" s="3">
-        <v>3100</v>
-      </c>
       <c r="H17" s="3">
+        <v>42400</v>
+      </c>
+      <c r="I17" s="3">
         <v>4500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4900</v>
-      </c>
-      <c r="M17" s="3">
-        <v>4000</v>
       </c>
       <c r="N17" s="3">
         <v>4000</v>
       </c>
       <c r="O17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P17" s="3">
         <v>3700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1300</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>1100</v>
       </c>
       <c r="AF17" s="3">
         <v>1100</v>
       </c>
       <c r="AG17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH17" s="3">
         <v>1000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3100</v>
-      </c>
       <c r="H18" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-4500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4900</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-4000</v>
       </c>
       <c r="N18" s="3">
         <v>-4000</v>
       </c>
       <c r="O18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="P18" s="3">
         <v>-3700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-1100</v>
       </c>
       <c r="AF18" s="3">
         <v>-1100</v>
       </c>
       <c r="AG18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2017,107 +2050,108 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E20" s="3">
         <v>15100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-15400</v>
       </c>
-      <c r="G20" s="3">
-        <v>17000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-17200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>13200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>15800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>21300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>8300</v>
       </c>
       <c r="N20" s="3">
         <v>8300</v>
       </c>
       <c r="O20" s="3">
+        <v>8300</v>
+      </c>
+      <c r="P20" s="3">
         <v>6100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>39400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-900</v>
       </c>
       <c r="AD20" s="3">
         <v>-900</v>
       </c>
       <c r="AE20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
@@ -2136,68 +2170,71 @@
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-22600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-20000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-12300</v>
       </c>
       <c r="N21" s="3">
         <v>-12300</v>
       </c>
       <c r="O21" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="P21" s="3">
         <v>-9800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6600</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-6900</v>
       </c>
       <c r="S21" s="3">
         <v>-6900</v>
       </c>
       <c r="T21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="U21" s="3">
         <v>-4900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2255,68 +2292,71 @@
       <c r="AO21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>900</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>800</v>
       </c>
       <c r="N22" s="3">
         <v>800</v>
       </c>
       <c r="O22" s="3">
+        <v>800</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2332,8 +2372,8 @@
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2374,151 +2414,157 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-22300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27600</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-13100</v>
       </c>
       <c r="N23" s="3">
         <v>-13100</v>
       </c>
       <c r="O23" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="P23" s="3">
         <v>-10400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>35800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-100</v>
       </c>
       <c r="F24" s="3">
         <v>-100</v>
       </c>
       <c r="G24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2534,8 +2580,8 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2544,29 +2590,29 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2400</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>4</v>
       </c>
@@ -2576,14 +2622,14 @@
       <c r="AC24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>0</v>
+      <c r="AD24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG24" s="3">
         <v>0</v>
@@ -2612,8 +2658,11 @@
       <c r="AO24" s="3">
         <v>0</v>
       </c>
+      <c r="AP24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2731,246 +2780,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-22500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-18500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27600</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-13100</v>
       </c>
       <c r="N26" s="3">
         <v>-13100</v>
       </c>
       <c r="O26" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="P26" s="3">
         <v>-10400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>33400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-22500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27600</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-13100</v>
       </c>
       <c r="N27" s="3">
         <v>-13100</v>
       </c>
       <c r="O27" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="P27" s="3">
         <v>-10400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>33400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3088,8 +3146,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3207,8 +3268,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3326,8 +3390,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3445,107 +3512,110 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-15100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>15400</v>
       </c>
-      <c r="G32" s="3">
-        <v>-17000</v>
-      </c>
       <c r="H32" s="3">
+        <v>22300</v>
+      </c>
+      <c r="I32" s="3">
         <v>17200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-13200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-15800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-21300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-8300</v>
       </c>
       <c r="N32" s="3">
         <v>-8300</v>
       </c>
       <c r="O32" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="P32" s="3">
         <v>-6100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>1500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-39400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1800</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>900</v>
       </c>
       <c r="AD32" s="3">
         <v>900</v>
       </c>
       <c r="AE32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF32" s="3">
         <v>400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2400</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
@@ -3564,127 +3634,133 @@
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-22500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27600</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-13100</v>
       </c>
       <c r="N33" s="3">
         <v>-13100</v>
       </c>
       <c r="O33" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="P33" s="3">
         <v>-10400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>33400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3802,251 +3878,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-22500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27600</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-13100</v>
       </c>
       <c r="N35" s="3">
         <v>-13100</v>
       </c>
       <c r="O35" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="P35" s="3">
         <v>-10400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>33400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
-      </c>
-      <c r="M38" s="2">
-        <v>45199</v>
       </c>
       <c r="N38" s="2">
         <v>45199</v>
       </c>
       <c r="O38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4088,8 +4173,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4131,127 +4217,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>97500</v>
+      </c>
+      <c r="E41" s="3">
         <v>64800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>107000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>35000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15500</v>
-      </c>
-      <c r="M41" s="3">
-        <v>18500</v>
       </c>
       <c r="N41" s="3">
         <v>18500</v>
       </c>
       <c r="O41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="P41" s="3">
         <v>11600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>26800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>35200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>26200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>31900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>36400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>8600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>16600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>15800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>5600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4369,8 +4459,11 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4381,7 +4474,7 @@
         <v>100</v>
       </c>
       <c r="F43" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="G43" s="3">
         <v>600</v>
@@ -4389,8 +4482,8 @@
       <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
+      <c r="I43" s="3">
+        <v>600</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
@@ -4410,8 +4503,8 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -4420,20 +4513,20 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>500</v>
-      </c>
-      <c r="T43" s="3">
-        <v>300</v>
       </c>
       <c r="U43" s="3">
         <v>300</v>
       </c>
       <c r="V43" s="3">
+        <v>300</v>
+      </c>
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
@@ -4446,8 +4539,8 @@
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -4488,8 +4581,11 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4499,12 +4595,12 @@
       <c r="E44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3">
         <v>800</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
@@ -4529,8 +4625,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4607,13 +4703,16 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>400</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -4639,68 +4738,68 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
-        <v>500</v>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="O45" s="3">
+        <v>500</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>700</v>
       </c>
       <c r="R45" s="3">
         <v>700</v>
       </c>
       <c r="S45" s="3">
+        <v>700</v>
+      </c>
+      <c r="T45" s="3">
         <v>1500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>200</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
-      </c>
       <c r="AD45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE45" s="3">
         <v>200</v>
       </c>
       <c r="AF45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG45" s="3">
         <v>100</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>200</v>
       </c>
       <c r="AH45" s="3">
         <v>200</v>
@@ -4709,185 +4808,191 @@
         <v>200</v>
       </c>
       <c r="AJ45" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK45" s="3">
         <v>100</v>
-      </c>
-      <c r="AK45" s="3">
-        <v>200</v>
       </c>
       <c r="AL45" s="3">
         <v>200</v>
       </c>
       <c r="AM45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AN45" s="3">
         <v>100</v>
       </c>
       <c r="AO45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E46" s="3">
         <v>68300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>108100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16900</v>
-      </c>
-      <c r="M46" s="3">
-        <v>20100</v>
       </c>
       <c r="N46" s="3">
         <v>20100</v>
       </c>
       <c r="O46" s="3">
+        <v>20100</v>
+      </c>
+      <c r="P46" s="3">
         <v>12300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>23800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>23700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>27800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>35900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>26800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>32400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>36600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>11800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>16800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>15900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E47" s="3">
         <v>51500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>59200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>63800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>59800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>61200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>68300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>54500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>43400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28100</v>
-      </c>
-      <c r="M47" s="3">
-        <v>21400</v>
       </c>
       <c r="N47" s="3">
         <v>21400</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3">
+        <v>21400</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4964,31 +5069,34 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>339600</v>
+      </c>
+      <c r="E48" s="3">
         <v>52100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>50400</v>
-      </c>
-      <c r="F48" s="3">
-        <v>50500</v>
       </c>
       <c r="G48" s="3">
         <v>50500</v>
       </c>
       <c r="H48" s="3">
+        <v>50500</v>
+      </c>
+      <c r="I48" s="3">
         <v>50600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>52500</v>
-      </c>
-      <c r="J48" s="3">
-        <v>13300</v>
       </c>
       <c r="K48" s="3">
         <v>13300</v>
@@ -4997,7 +5105,7 @@
         <v>13300</v>
       </c>
       <c r="M48" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="N48" s="3">
         <v>13400</v>
@@ -5009,13 +5117,13 @@
         <v>13400</v>
       </c>
       <c r="Q48" s="3">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="R48" s="3">
         <v>13500</v>
       </c>
       <c r="S48" s="3">
-        <v>13600</v>
+        <v>13500</v>
       </c>
       <c r="T48" s="3">
         <v>13600</v>
@@ -5024,10 +5132,10 @@
         <v>13600</v>
       </c>
       <c r="V48" s="3">
-        <v>0</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>4</v>
+        <v>13600</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>4</v>
@@ -5041,8 +5149,8 @@
       <c r="AA48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -5083,8 +5191,11 @@
       <c r="AO48" s="3">
         <v>0</v>
       </c>
+      <c r="AP48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5202,8 +5313,11 @@
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5321,8 +5435,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5440,8 +5557,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5460,20 +5580,20 @@
       <c r="H52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>400</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
+      <c r="M52" s="3">
+        <v>400</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
@@ -5487,8 +5607,8 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -5559,8 +5679,11 @@
       <c r="AO52" s="3">
         <v>0</v>
       </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5678,127 +5801,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>496200</v>
+      </c>
+      <c r="E54" s="3">
         <v>172000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>217700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>153100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>147400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>133900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>158300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>93600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>66200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>58600</v>
-      </c>
-      <c r="M54" s="3">
-        <v>54900</v>
       </c>
       <c r="N54" s="3">
         <v>54900</v>
       </c>
       <c r="O54" s="3">
+        <v>54900</v>
+      </c>
+      <c r="P54" s="3">
         <v>25700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>37300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>41500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>36000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>26800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>36600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>16800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>15900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>5900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5840,8 +5969,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5883,104 +6013,105 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
-      </c>
-      <c r="M57" s="3">
-        <v>2100</v>
       </c>
       <c r="N57" s="3">
         <v>2100</v>
       </c>
       <c r="O57" s="3">
-        <v>200</v>
+        <v>2100</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
       </c>
       <c r="Q57" s="3">
+        <v>200</v>
+      </c>
+      <c r="R57" s="3">
         <v>1200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>600</v>
       </c>
       <c r="S57" s="3">
         <v>600</v>
       </c>
       <c r="T57" s="3">
+        <v>600</v>
+      </c>
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
       <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
       <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
         <v>1900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>100</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
-      </c>
       <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="3">
         <v>200</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>100</v>
       </c>
       <c r="AD57" s="3">
         <v>100</v>
       </c>
       <c r="AE57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF57" s="3">
         <v>200</v>
       </c>
-      <c r="AF57" s="3">
-        <v>0</v>
-      </c>
       <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
         <v>200</v>
       </c>
-      <c r="AH57" s="3">
-        <v>0</v>
-      </c>
       <c r="AI57" s="3">
         <v>0</v>
       </c>
@@ -5991,60 +6122,63 @@
         <v>0</v>
       </c>
       <c r="AL57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="3">
         <v>100</v>
       </c>
-      <c r="AM57" s="3">
-        <v>0</v>
-      </c>
       <c r="AN57" s="3">
         <v>0</v>
       </c>
       <c r="AO57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>24700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>42600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>34900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>29900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7900</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2000</v>
       </c>
       <c r="N58" s="3">
         <v>2000</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
+        <v>2000</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
@@ -6055,14 +6189,14 @@
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T58" s="3">
-        <v>6300</v>
+      <c r="T58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U58" s="3">
         <v>6300</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
+      <c r="V58" s="3">
+        <v>6300</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>4</v>
@@ -6079,8 +6213,8 @@
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -6121,94 +6255,97 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E59" s="3">
         <v>67000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>73000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>60600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>55500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>31000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2700</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>200</v>
       </c>
       <c r="AB59" s="3">
         <v>200</v>
       </c>
       <c r="AC59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD59" s="3">
         <v>300</v>
       </c>
       <c r="AE59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AF59" s="3">
         <v>100</v>
@@ -6217,13 +6354,13 @@
         <v>100</v>
       </c>
       <c r="AH59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI59" s="3">
         <v>200</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK59" s="3">
         <v>100</v>
@@ -6238,108 +6375,111 @@
         <v>100</v>
       </c>
       <c r="AO59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E60" s="3">
         <v>76300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>95200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>91000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>75800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>80500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>50500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13100</v>
-      </c>
-      <c r="M60" s="3">
-        <v>5000</v>
       </c>
       <c r="N60" s="3">
         <v>5000</v>
       </c>
       <c r="O60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P60" s="3">
         <v>2300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>300</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>400</v>
       </c>
       <c r="AD60" s="3">
         <v>400</v>
       </c>
       <c r="AE60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF60" s="3">
         <v>200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>100</v>
-      </c>
-      <c r="AG60" s="3">
-        <v>300</v>
       </c>
       <c r="AH60" s="3">
         <v>300</v>
       </c>
       <c r="AI60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AJ60" s="3">
         <v>100</v>
@@ -6354,64 +6494,67 @@
         <v>100</v>
       </c>
       <c r="AN60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO60" s="3">
         <v>200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E61" s="3">
         <v>29900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>39000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>35400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>36800</v>
-      </c>
-      <c r="M61" s="3">
-        <v>32900</v>
       </c>
       <c r="N61" s="3">
         <v>32900</v>
       </c>
       <c r="O61" s="3">
+        <v>32900</v>
+      </c>
+      <c r="P61" s="3">
         <v>25500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>19300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>19200</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -6478,49 +6621,52 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E62" s="3">
         <v>40100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>43700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>41900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>45000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>30200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>46800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>36300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>32100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23300</v>
-      </c>
-      <c r="M62" s="3">
-        <v>6000</v>
       </c>
       <c r="N62" s="3">
         <v>6000</v>
       </c>
       <c r="O62" s="3">
+        <v>6000</v>
+      </c>
+      <c r="P62" s="3">
         <v>2700</v>
-      </c>
-      <c r="P62" s="3">
-        <v>3300</v>
       </c>
       <c r="Q62" s="3">
         <v>3300</v>
@@ -6538,7 +6684,7 @@
         <v>3300</v>
       </c>
       <c r="V62" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="W62" s="3">
         <v>1200</v>
@@ -6549,8 +6695,8 @@
       <c r="Y62" s="3">
         <v>1200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
+      <c r="Z62" s="3">
+        <v>1200</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>4</v>
@@ -6567,8 +6713,8 @@
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF62" s="3">
-        <v>0</v>
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
@@ -6597,8 +6743,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6716,8 +6865,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6835,8 +6987,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6954,106 +7109,109 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>174700</v>
+      </c>
+      <c r="E66" s="3">
         <v>146900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>169800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>155500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>167900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>132600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>168500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>131500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>73100</v>
-      </c>
-      <c r="M66" s="3">
-        <v>43800</v>
       </c>
       <c r="N66" s="3">
         <v>43800</v>
       </c>
       <c r="O66" s="3">
+        <v>43800</v>
+      </c>
+      <c r="P66" s="3">
         <v>30400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>24900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>24000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>300</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>400</v>
       </c>
       <c r="AD66" s="3">
         <v>400</v>
       </c>
       <c r="AE66" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF66" s="3">
         <v>200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>100</v>
-      </c>
-      <c r="AG66" s="3">
-        <v>300</v>
       </c>
       <c r="AH66" s="3">
         <v>300</v>
       </c>
       <c r="AI66" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AJ66" s="3">
         <v>100</v>
@@ -7068,13 +7226,16 @@
         <v>100</v>
       </c>
       <c r="AN66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO66" s="3">
         <v>200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7116,8 +7277,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7235,8 +7397,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7354,8 +7519,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7473,8 +7641,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7592,127 +7763,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-227500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-213200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-189100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-183700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-199600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-177100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-187800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-178100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-159500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-139000</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-111400</v>
       </c>
       <c r="N72" s="3">
         <v>-111400</v>
       </c>
       <c r="O72" s="3">
+        <v>-111400</v>
+      </c>
+      <c r="P72" s="3">
         <v>-98300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-79900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-65600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-58500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-51300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-44500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-39600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-35000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-33200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-28700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-25500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-58900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-54400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-51500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-49700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-47500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-46100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-44200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-41300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-37500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-36600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-35800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-35100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-34300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-33800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-33200</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7830,8 +8007,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7949,8 +8129,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8068,127 +8251,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>321500</v>
+      </c>
+      <c r="E76" s="3">
         <v>25100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>47800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-2400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-20500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-10200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-37900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-34000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-14500</v>
-      </c>
-      <c r="M76" s="3">
-        <v>11000</v>
       </c>
       <c r="N76" s="3">
         <v>11000</v>
       </c>
       <c r="O76" s="3">
+        <v>11000</v>
+      </c>
+      <c r="P76" s="3">
         <v>-4800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>27300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>31000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>34500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>24400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>28800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>31100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>16800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8306,251 +8495,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
-      </c>
-      <c r="M80" s="2">
-        <v>45199</v>
       </c>
       <c r="N80" s="2">
         <v>45199</v>
       </c>
       <c r="O80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-22500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27600</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-13100</v>
       </c>
       <c r="N81" s="3">
         <v>-13100</v>
       </c>
       <c r="O81" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="P81" s="3">
         <v>-10400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>33400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8592,8 +8790,9 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8651,8 +8850,8 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>4</v>
@@ -8669,8 +8868,8 @@
       <c r="AA83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -8711,8 +8910,11 @@
       <c r="AO83" s="3">
         <v>0</v>
       </c>
+      <c r="AP83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8830,8 +9032,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8949,8 +9154,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9068,8 +9276,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9187,8 +9398,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9306,127 +9520,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-34500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>23300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>28600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5900</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-3600</v>
       </c>
       <c r="N89" s="3">
         <v>-3600</v>
       </c>
       <c r="O89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="P89" s="3">
         <v>-1100</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-5300</v>
       </c>
       <c r="Q89" s="3">
         <v>-5300</v>
       </c>
       <c r="R89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="S89" s="3">
         <v>-4700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-100</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-200</v>
       </c>
       <c r="AE89" s="3">
         <v>-200</v>
       </c>
       <c r="AF89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-200</v>
-      </c>
-      <c r="AH89" s="3">
-        <v>-300</v>
       </c>
       <c r="AI89" s="3">
         <v>-300</v>
       </c>
       <c r="AJ89" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AK89" s="3">
         <v>-200</v>
       </c>
       <c r="AL89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AM89" s="3">
         <v>-400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9468,25 +9688,26 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -9506,11 +9727,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -9527,8 +9748,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
@@ -9545,8 +9766,8 @@
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -9587,8 +9808,11 @@
       <c r="AO91" s="3">
         <v>0</v>
       </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9706,8 +9930,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9825,104 +10052,107 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E94" s="3">
         <v>900</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-200</v>
       </c>
       <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-4700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7400</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-27000</v>
       </c>
       <c r="N94" s="3">
         <v>-27000</v>
       </c>
       <c r="O94" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="P94" s="3">
         <v>-6700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-7800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6600</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-2500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>31000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-900</v>
       </c>
       <c r="AD94" s="3">
         <v>-900</v>
       </c>
       <c r="AE94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI94" s="3" t="s">
         <v>4</v>
       </c>
@@ -9935,8 +10165,8 @@
       <c r="AL94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM94" s="3">
-        <v>0</v>
+      <c r="AM94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN94" s="3">
         <v>0</v>
@@ -9944,8 +10174,11 @@
       <c r="AO94" s="3">
         <v>0</v>
       </c>
+      <c r="AP94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9987,8 +10220,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10028,8 +10262,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10106,8 +10340,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10225,8 +10462,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10344,8 +10584,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10463,82 +10706,85 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>47500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>30700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>10200</v>
-      </c>
-      <c r="M100" s="3">
-        <v>37500</v>
       </c>
       <c r="N100" s="3">
         <v>37500</v>
       </c>
       <c r="O100" s="3">
+        <v>37500</v>
+      </c>
+      <c r="P100" s="3">
         <v>16600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5600</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>19800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>10900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-900</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>3200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>4</v>
+      <c r="AA100" s="3">
+        <v>0</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>4</v>
@@ -10546,8 +10792,8 @@
       <c r="AC100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
+      <c r="AD100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
@@ -10562,28 +10808,31 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AL100" s="3">
-        <v>0</v>
+      <c r="AL100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AM100" s="3">
         <v>0</v>
       </c>
-      <c r="AN100" s="3" t="s">
-        <v>4</v>
+      <c r="AN100" s="3">
+        <v>0</v>
       </c>
       <c r="AO100" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP100" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10623,8 +10872,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10701,123 +10950,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-42100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>70500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M102" s="3">
-        <v>6900</v>
       </c>
       <c r="N102" s="3">
         <v>6900</v>
       </c>
       <c r="O102" s="3">
+        <v>6900</v>
+      </c>
+      <c r="P102" s="3">
         <v>8700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>33400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>10900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>4700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-100</v>
       </c>
     </row>
